--- a/docs/custom-views/Custom Views - Spec v3 Test Cases.xlsx
+++ b/docs/custom-views/Custom Views - Spec v3 Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software Testing\Automation\Agentex Installation\Agentex Installation\docs\custom-views\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BD37DA-D0B8-471C-AE16-B855DBEC6525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F83A2B8-43C1-4143-A8E9-90DE6E816FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4662" uniqueCount="2010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4662" uniqueCount="2107">
   <si>
     <t>Feature</t>
   </si>
@@ -7317,397 +7317,688 @@
     <t/>
   </si>
   <si>
-    <t>execu_2026-10-04_17-47-37 (High/Urgent run)</t>
-  </si>
-  <si>
     <t>Failed</t>
   </si>
   <si>
-    <t>Bug: NDC-1947</t>
-  </si>
-  <si>
     <t>Inconclusive</t>
   </si>
   <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Failed (High). Request 1 (no Authorization header) -&gt; 401 TOKEN_MISSING 'Authorization token is required.', no data (ok); a malformed bearer -&gt; 401 TOKEN_INVALID (ok). Request 2 (expired token): a fresh login token (JWT iat 15:14:38Z, exp 15:19:38Z = 5 min), never refreshed, was sent at 15:22:55Z (server Date header; server and local clocks agree within 1 s) -&gt; 200 OK with the full Leads view list, 197 s after its exp. After POST /iam/auth/logout the same token -&gt; 401 SESSION_REVOKED. So access-token expiry is not enforced; only session revocation stops a token. One clean observation: two other probe tokens … | Defect: API accepts expired access tokens (JWT exp not enforced) as long as the session is alive</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. With bearer + x-tenant-id: 200, 96 Leads list views. Without x-tenant-id: 200, the identical 96 views (same ids). Recorded behaviour: the header is not required - the tenant comes from the token. Extra: a different tenant id (…0003) and a non-UUID value in x-tenant-id were also ignored and returned the same NDC-Staging views; no request returned another tenant's data.</t>
-  </si>
-  <si>
-    <t>execu_2026-10-04_12-29-38 (Low/Medium run)</t>
-  </si>
-  <si>
-    <t>No workspace with custom views turned off exists, and none can be made: in CRM the customViewsEnabled flag comes from a build-time feature flag hard-coded to true (featureFlags-Bty4zi8j.js). Only the Desk workspace provider passes customViewsEnabled:false. The message key views.list.unavailable (title 'Custom views are not available', body 'Custom views are turned off for this workspace.') exists…</t>
-  </si>
-  <si>
     <t>Not tested (feature missing)</t>
   </si>
   <si>
-    <t>Search' -&gt; Created by me: QA CV Search Alpha, QA CV Search Public. 'qa cv search alpha' -&gt; QA CV Search Alpha (case ignored). 'عملاء' -&gt; QA CV عملاء. 'zzqq-no-match' -&gt; 'No views match.'. Cleared -&gt; all four groups restored. Extra term 'leads' filtered across Pinned views, Shared with me and Public views at once. Note: the precondition's 'QA CV Search Public' (Public) cannot be set up as written…</t>
-  </si>
-  <si>
-    <t>openListViewIds keeps IDs of deleted views; a view can be both open and recently closed</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-B03-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>QA CV pinned' opened as a tab; tab menu offered Pin view; after pinning, the picker lists it under Pinned views and Created by me, both 'Show as tab' checkboxes are disabled and aria-checked=true; a forced click left it ticked and the tab stayed visible. The wrapper's title tooltip reads exactly 'Pinned views always show as tabs. Unpin the view to hide its tab.' Observation: the message is only …</t>
-  </si>
-  <si>
-    <t>All 11 'QA CV close' views ticked as tabs. Close view on 'QA CV close01' -&gt; Recently closed: [QA CV close01, Today's Leads*, My Leads*]. After closing close02…close11 -&gt; Recently closed shows exactly 10: close11 … close02 (close01, the oldest, dropped); recentlyClosedListViewIds holds the same 10 IDs in the same order. The 11 closed tabs left the tab bar.</t>
-  </si>
-  <si>
-    <t>Start: dropdown (pref listPickerMode=dropdown). 'Show custom views as tabs' -&gt; tab bar with 7 tabs, pref=tabs; after reload still tabs. 'Show custom views as a dropdown' -&gt; 'Custom views' dropdown button, pref=dropdown; after reload still dropdown. Switched back to tabs and reloaded -&gt; tabs (7). No console errors. (Spec order was tabs-&gt;dropdown-&gt;tabs; the account started in dropdown, so both dire…</t>
-  </si>
-  <si>
     <t>A standard view offers only Edit, Pin/Unpin, Clone, Delete View</t>
   </si>
   <si>
-    <t>Selected 'QA CV x' in Leads; GET list-preferences lastListViewId = f9bda6a3-… (the ID of 'QA CV x'). Signed out via profile -&gt; Logout (landed on /login?reason=revoked). Signed in again and opened Leads: 'QA CV x' is the selected tab.</t>
-  </si>
-  <si>
-    <t>Leads -&gt; tab 'QA CV x'; Deals -&gt; 'All Deals' (Deals is in dropdown mode); Leads again -&gt; 'QA CV x'; Deals again -&gt; 'All Deals'. list-preferences: Leads lastListViewId = QA CV x, Deals lastListViewId = 9707b09e-… (All Deals). Each module keeps its own last view.</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Failed (Low). Shared/foreign views were made by ALT1 (creator profile does not matter here). Own 'QA CV x' -&gt; opens, tab selected. 'QA CV shared-to-me' (ALT1, shared with OWNER) -&gt; opens, 9 records. Deleted 'QA CV gone' and ALT1's private 'QA CV user-private' (both API 404 for OWNER) -&gt; ?view= is stripped, a toast says 'That view is no longer available. Showing your default view.', nothing of the view is shown, no console errors, no failed API calls. FAIL: the fallback is not All Leads - both land on 'QA CV tab2' and lastListViewId is rewritten to it (it was 'QA CV shared-to-me' a moment before), so the 'de… | Defect: ?view= with a deleted or foreign view id falls back to an arbitrary view ('QA CV tab2') instead of All Leads and overwrites the last-used view ; Deep link ?view= to a view of a non-default layout is dropped on a full page load</t>
-  </si>
-  <si>
-    <t>List preferences changed in two browser tabs: the later write silently overwrites the earlier one (lost update)</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-B15-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Failed (Low). D1 '' and D2 '   ': Save is silently disabled and 'Enter a name for the view.' is never shown (Zoho keeps Save enabled and shows 'Custom view name cannot be empty.'). D5 (121 chars): input maxlength=120 cuts the 121st char silently, so 'A view name can be at most 120 characters.' never appears - same pattern as Zoho (maxlength=100); the API alone enforces it (121 chars -&gt; 422 too_long). D3 'Q', D4 (120), D8 Arabic, D9 (RLM kept), D10 emoji/astral saved exactly as typed. D6 stored trimmed ('QA CV trim'). D7 'qa cv NAME' refused as duplicate of 'QA CV name' (409 VIEW_NAME_TAKEN, names are case-i… | Defect: Empty or spaces-only view name: Save is silently disabled, 'Enter a name for the view.' is never shown</t>
-  </si>
-  <si>
-    <t>QA CV dup' created first (API, 201). New custom view with the same name -&gt; Save blocked with alert 'You already have a view with this name.'; POST returned 409 VIEW_NAME_TAKEN. Only one 'QA CV dup' exists, row_version still 1.</t>
-  </si>
-  <si>
-    <t>Run as a second user CRM_USER_ALT1 (it now signs in fully — the 'stuck on Signing in…' blocker in spec §1.4 is gone — choosing organisation 'Anyware' = NDC-Staging tenant a7a7a7a7-…0004). Note: ALT1's profile is Admin, not the User profile the case names; the rule under test (name unique per owner) does not depend on profile. ALT1 saved 'QA CV dup' -&gt; 201, toast 'Custom view "QA CV dup" created.'…</t>
-  </si>
-  <si>
-    <t>Rule recorded: view names are unique per owner AND per kind. As OWNER the queue POST could not reach the name check - 409 WORKQUEUE_LIMIT ('You already have 15 work queues') because the owner already owns 15 queues on NDC-Staging; list 'QA CV k' was created (201). Re-run as ALT1: list 'QA CV k' 201 and queue 'QA CV k' 201 - both allowed; GET ?kind=list returns only the list, GET ?kind=queue retur…</t>
-  </si>
-  <si>
-    <t>Row Company · Contains · (empty), name 'QA CV incomplete', Save clicked -&gt; blocked with alert 'Complete this row (field, operator and value) or remove it.'; no POST was sent; GET shows no 'QA CV incomplete'. Text operators offered: Contains, Does not contain, Equals, Not equal to, Starts with, Ends with, Is empty, Is not empty.</t>
-  </si>
-  <si>
-    <t>Run on layout 'New Layout' (Standard has no checkbox field and 'New Layout' has no Company field): rows Single Line · Is empty, Created At · Today, Use Wallet Number · Is true. No value input appeared for any row; Save -&gt; 201, toast 'Custom view "QA CV no-value" created.'; stored conditions have value null with operators is_empty / today / is_true. Results: with lead QA CV L13 (created today, wal…</t>
-  </si>
-  <si>
-    <t>UI: 25 rows (Full Name · Is not empty) added; 'Add criteria row' became disabled with title 'A maximum of 25 criteria rows is allowed'; the 25-row view saved (201, toast 'Custom view "QA CV 25-rows" created.'), GET shows 25 conditions. API: POST with 26 conditions -&gt; 422 INVALID_VIEW, details settings.criteria too_many 'At most 25 criteria rows are allowed.'; no 'QA CV 26-rows' exists.</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Failed (Low). Editor (Standard layout): added Company, Created At, Email, Full Name, Last Activity, Lead Owner, Lead Status, Phone, then reordered with Move up to Full Name, Lead Status, Company, Email, Phone, Lead Owner, Created At, Last Activity ('Modified Time' is not offered on the Standard layout; Last Activity = last_modified_at). POST columns in that exact order -&gt; 201. Grid after reload: Full Name, Lead Status, Company, Email, Phone, Lead Owner, Created At, Last Activity - order correct - but two unchosen columns, Tags and Source, are appended. Manage Columns panel says 'VISIBLE (8)' and lists only … | Defect: Grid appends unchosen Tags and Source columns to a view with a chosen column list; Manage Columns says 8 while 10 are shown</t>
-  </si>
-  <si>
-    <t>Editor shows 'No columns chosen: everyone sees their usual columns.'; 'QA CV no-columns' saved with columns []. Its grid shows the owner's usual columns (list-preferences visibleKeys first_name, phone, lead_status, owner, created_at, last_modified_at + Tags, Source; Email is in the owner's hiddenKeys). All Leads differs only because it has its own saved columns (includes email), so the comparison…</t>
-  </si>
-  <si>
-    <t>Layout FieldPermissions. No tip at 10 columns; at 11 the editor shows 'Tip: more than 10 columns makes the table hard to read.'. All available fields added -&gt; 30 columns, saved (201, toast). API: PATCH with 30 columns -&gt; 200; PATCH with 31 -&gt; 422 INVALID_VIEW settings.columns too_many 'A view may show at most 30 columns.'; GET still 30.</t>
-  </si>
-  <si>
-    <t>Page size 200 accepted by the server but not offered in the editor; with 200 stored, the grid's Rows per page shows 10 and the editor shows 'Select…'</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-C12-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>QA CV no-users', Share with = Selected users, no user picked, Save -&gt; alert 'Choose at least one user, or share with everyone instead.'; no view created. The client did send the POST, the server refused it (422). Direct API POST visibility 'selected' with shared_user_ids [] -&gt; 422 INVALID_VIEW shared_user_ids required 'Select at least one user to share this view with, or choose a different visi……</t>
-  </si>
-  <si>
-    <t>Filter panel: Lead Status · Equals · Busy -&gt; 1–16 of 16. New custom view: notice 'The criteria start with the filters applied on the records page.', 'Filter by criteria' ticked, row Leads · Lead Status · Equals · Busy. Saved 'QA CV from-filter' (stored criteria lead_status equals Busy). Opened on its own (no filter in the URL) it returns the same 16 records. Observation: right after saving, the l…</t>
-  </si>
-  <si>
-    <t>List-view count before: 35. Filled name 'QA CV discard', a criteria row and a column, then Cancel (bottom) -&gt; back to Leads, no POST. Repeated with the top back/Cancel control -&gt; back to Leads, no POST. Count after: 35; no 'QA CV discard'. (No 'discard changes?' prompt is shown — not required by the case.)</t>
-  </si>
-  <si>
-    <t>UI: double-click Save on 'QA CV double' sent two POSTs - first 201, second 409 VIEW_NAME_TAKEN; toast 'Custom view "QA CV double" created.'; one view exists. API: two parallel POSTs 'QA CV double-api' -&gt; 201 and 409 VIEW_NAME_TAKEN; one view exists. Observation: the Save button is not disabled while the request is in flight - only the server's duplicate-name rule prevents a second view.</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. 'QA CV partial' created with criteria (2 rows), 8 columns, sort created_at asc, page size 50. PATCH {name:'QA CV partial-2', row_version} -&gt; 200. GET after: only name, row_version and last_modified_at changed; settings, visibility and shared_user_ids identical.</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. PATCH with is_system:true, owner_user_id:&lt;ALT1&gt;, category:public_views + can_edit:false, row_version:999 -&gt; each 200 and the key ignored: GET shows is_system false, owner/created_by unchanged, category created_by_me, can_edit/can_delete true. row_version only advanced by the normal +1 per save (the body's row_version is ignored). The concurrency key is expected_row_version (what the editor sends): expected_row_version:1 when current is 9 -&gt; 409 VERSION_CONFLICT, nothing changed. Observation: a PATCH that omits expected_row_version is accepted without any version check (last write wins).</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. name 12345 / ['QA CV arr'] / {x:1} -&gt; 400 VALIDATION_ERROR; name null -&gt; 422; columns 'name' / {a:1} -&gt; 422; criteria 'status=1' / [] / 7 -&gt; 422; page_size '25' / [25] / {n:25} -&gt; 422 (also 0 and 500 -&gt; 422). No 500 anywhere, no partial view. Two nulls in the test data are valid per the contract and were accepted as 'not set': columns:null -&gt; 201, stored as [] (= 'No columns chosen'); page_size:null -&gt; 201 (contract: page_size|null). Suggest removing those two values from the case. Observation: 422 bodies only say 'The view is not valid.' with no field detail.</t>
-  </si>
-  <si>
-    <t>Editor filled ('QA CV expiry', criteria Full Name · Is not empty, 2 columns) and left open 5 min 35 s. The app refreshed the token in the background (POST /iam/auth/refresh 200 at 11:31:57Z). Save at 11:34:34Z -&gt; 201, view stored with 1 condition and 2 columns; name field still filled before save. No data lost, no sign-in prompt needed.</t>
-  </si>
-  <si>
     <t>Not Run</t>
   </si>
   <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. Operator lists read in the editor for 21 fields (Leads Standard: Company, Lead Status, Owner, Source, Tags, Review Status, Created At, Lead Source; Leads FieldPermissions: Date, Date Time, Checkbox, Multi Select, Lookup, Pick List, Number, Currency Permission; Deals: Amount, Stage, Pipeline, Closing date, Account) and in the Filter panel for the same fields - every list is identical (same operators, same order). Against spec §2.3: Text (Company) = the 8 listed; Number/Currency/Amount = equals, not_equal_to, greater_than, less_than, &gt;=, &lt;=, is_empty, is_not_empty (no between); Date = the listed…</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. Seeds (Standard layout): L01 'QA CV Acme', L02 'qa cv acme', L03 'شركة الأمل', L04 'QA CV Rocket 🚀', L05 'QA​CV Zero', L06 empty (other QA CV leads empty). 'QA CV text-sweep' built in the editor (Full Name starts with 'QA CV' + Company &lt;op&gt; &lt;value&gt;); one UI save per value (D3 starts_with, D6/D7/D12 equals, D8/D14 contains, D10 ends_with) - the PATCH body and GET carry the value byte-exact (D6 spaces kept, U+200B kept, emoji U+1F680, Arabic). Full 6 operators x 7 values via PATCH: in all 42 cases grid (records?view_id) == module filter (records?filters=, the call the Filter panel makes). Rules…</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. Seeds: L01 Comment never set (null), L02 '' (set to 'x', then cleared - stored as an empty string), L03 '   ', L04 'Call back' (L09 also '   ' from an earlier run). 'QA CV text-empty' built in the editor (Full Name starts with 'QA CV' + Comment Is empty) -&gt; 13 records; edited in the editor to Is not empty -&gt; 3. Rule recorded: null and '' match is_empty; whitespace-only ('   ') does NOT (it matches is_not_empty). is_empty: H01q,L01,L02,L05,L06,L07,L08,L10,L11,L12,L13,L14,L15; is_not_empty: L03,L04,L09 - exact complement (13+3 = 16 QA CV leads), L04 never in is_empty, and both identical to the m…</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. Seeds already in place: D01 0, D02 9999.99, D03 10000, D04 10000.01, D05 empty, D06 -1, D07 15000, D08 1000000000 (+ D09 empty). 'QA CV amount-bounds' built in the Deals editor (Deal name starts with 'QA CV' + Amount equals 10000) -&gt; 1; edited in the editor through every operator (ids: not_equal_to, greater_than, less_than, greater_than_or_equal_to, less_than_or_equal_to). equals 10000 -&gt; D03; not_equal_to -&gt; D01,D02,D04,D05,D06,D07,D08,D09 (empty amounts included, same as the module filter); greater_than -&gt; D04,D07,D08; less_than -&gt; D01,D02,D06; &gt;= -&gt; D03,D04,D07,D08; &lt;= -&gt; D01,D02,D03,D06; e…</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Failed (Medium). Editor (Amount box is input type=number): '15,000' -&gt; the browser drops the comma, saved as '15000' -&gt; D07 (ok). '١٥٠٠٠' and 'abc' -&gt; box stays empty, Save shows 'Complete this row (field, operator and value) or remove it.' (ok, blocked with a message). '-1' -&gt; D06 (ok). FAIL '1e9' -&gt; saved as the string '1e9' (not normalised, not rejected) and the view returns 0 records although D08 = 1000000000. API: POST with value '15,000', '١٥٠٠٠', '1e9' and 'abc' -&gt; all 201 Created, the raw string is stored and the view matches 0 records (module filter also 0); expected 400/422 for 'abc' and normalise-or… | Defect: Number criteria accept non-numeric values ('1e9' in the editor; 'abc', '15,000', Arabic digits via API) and silently match nothing</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. 'QA CV amount-empty' built in the Deals editor (Deal name starts with 'QA CV' + Amount is empty), then edited to is not empty and equals 0. is_empty -&gt; D05, D09 (both have no amount; D09 is an extra empty-amount deal from an earlier run); is_not_empty -&gt; D01 (0), D02, D03, D04, D06, D07, D08 - never D05; equals 0 -&gt; D01 only, never D05/D09. Grid == module filter for all three.</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. Run on the FieldPermissions layout (Date Permission only exists there). First seeds (H01-H04/N01) were deleted mid-case by the parallel morning run's cleanup, so the case was re-run on fresh seeds QA CV R01-R10 (R01 = D-6 28 Sep, R02 = D-5 29 Sep, R03 = D-2 2 Oct, R04 = D 4 Oct, R05 = D+1 5 Oct, R06-R10 empty; D = 4 Oct 2026 Cairo). 'QA CV date-abs' built and edited in the editor (between uses two date inputs 'from'/'to', stored as [from,to]). is D -&gt; R04; is_before D -&gt; R01,R02,R03; is_after D -&gt; R05; is_between D-5..D -&gt; R02,R03,R04 (bounds inclusive); is_not_between D-5..D -&gt; R01,R05; is_be…</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Failed (High). FieldPermissions seeds (Date Time Permission, stored UTC, shown by the app in Cairo UTC+3): R01 = 3 Oct 23:50, R02 = 4 Oct 00:10, R03 = 4 Oct 23:50, R04 = 5 Oct 00:10 Cairo. 'QA CV date-rel' built in the editor (Name starts with 'QA CV' + Date Time Permission Today). Grid (records?view_id) == module filter at every check. 19:10 Cairo 4 Oct: today -&gt; R03,R04 (expected R02,R03); yesterday -&gt; R01,R02 (expected R01); tomorrow -&gt; none (expected R04); the grid shows R04 as '05/10/2026 12:10 AM' inside the Today view. 23:50 Cairo 4 Oct: same (today R03,R04; yesterday R01,R02; tomorrow none). 00:10 Cairo 5 Oct: same again - expected today R04, yesterday R02,R03, tomorrow none; the results did not mo | Defect: today / yesterday / tomorrow criteria cut days at UTC midnight instead of the tenant's Cairo time</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. FieldPermissions layout, seeds R01-R10, D = Sun 4 Oct 2026 (Cairo). Week-start probe (26 Sep-12 Oct spread): this_week -&gt; 28 Sep (Mon) .. 4 Oct (Sun) -&gt; the build's week starts on MONDAY. Case seeds: R01 27 Sep (last day of last week), R02 28 Sep (first day of this week), R03 4 Oct (last day of this week), R04 5 Oct (first day of next week), R05 30 Sep (last day of last month), R06 1 Oct, R07 1 Nov, R08 31 Dec 2025, R09 1 Jan 2026, R10 1 Jan 2027. 'QA CV date-cal' built in the editor with This week. this_week -&gt; R02,R03,R05,R06; last_week -&gt; R01; next_week -&gt; R04; this_month -&gt; R03,R04,R06; la…</t>
-  </si>
-  <si>
-    <t>Layout FieldPermissions, field Date Permission (date_3_9). UI (24 saves) and API (24 POSTs) agree: In the last N days / In the next N days accept 1 and 3650, reject 0, 3651, -1, 1.5 (lower bound 1; input min=1 max=3650 step=1). Age in days / Due in days accept 0, 1, 3650, reject 3651, -1, 1.5 (lower bound 0; min=0). Rejected values: UI save blocked, API 422, no view created. Cross-check with QA C…</t>
-  </si>
-  <si>
-    <t>Seeds in layout FieldPermissions, Date Time Permission: H01 now-30m, H02 now-2h, H03 now+30m, H04 now+2h (now = 11:51:06Z). Row 1 uses 'Name starts with QA CV H' (the FieldPermissions layout has 'Name', not First Name). last_n_hours 1 -&gt; H01; 720 -&gt; H01,H02; next_n_hours 1 -&gt; H03; 720 -&gt; H03,H04 (API filter and grid counts 1/2/1/2 agree). 721 blocked in the editor; API 721 and 0 -&gt; 422 'filters[1…</t>
-  </si>
-  <si>
-    <t>Seeds N01 now-1h, N02 now+1h, N03 empty (layout FieldPermissions). before_now -&gt; N01 only; after_now -&gt; N02 only; N03 in neither. Views saved from the editor; grid counts (1 and 1) equal the API filter. Observation: opening a view of another layout by link (?view=…) while the page is on Standard shows an empty tab bar and '0 records' with no explanation.</t>
-  </si>
-  <si>
-    <t>Seeds (layout FieldPermissions): K01 Checkbox Permission true, K02 false, K03 never set. Views saved from the editor with 'Name starts with QA CV K' + Checkbox Permission: Is true -&gt; K01 (grid 1 record); Is false -&gt; K02, K03 (grid 2 records). Recorded rule: a never-set checkbox counts as false. Grid and API filter agree.</t>
-  </si>
-  <si>
-    <t>A pick list value removed from the field is not shown in the view editor (blank 'Value' placeholder, no warning), although the view still filters on it</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-D14-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. Deviation: Multi Select Permission has only two options ('1','2'), so A='1', B='2' and the case's L04 {C} could not be seeded. Seeds R01 {1}, R02 {1,2}, R03 {2}, R04-R10 empty. 'QA CV multiselect' built in the editor (options are checkboxes) with contains any of 1,2 -&gt; 3. contains_any_of [1,2] -&gt; R01,R02,R03; contains_all_of [1,2] -&gt; R02 only; contains_none_of [1,2] -&gt; R04..R10 (empty values count as 'none of', same as module filter); is_empty -&gt; R04..R10 (7); is_not_empty -&gt; R01,R02,R03; extra: any_of [1] -&gt; R01,R02, all_of [1] -&gt; R01,R02, none_of [1] -&gt; R03..R10. Grid == module filter in eve…</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Failed (Medium). Seeds (FieldPermissions): R01 -&gt; Contact X 'lead01', R02 -&gt; X, R03 -&gt; Contact Y 'lead02', R04-R10 empty. Editor: Lookup Permission offers Equals / Not equal to / Is empty / Is not empty, but the value control for Equals is a plain text box ('Value'), with no record search or picker and no suggestions while typing. Typing the record name 'lead01' saves value 'lead01' literally and the view shows 0 records (R01/R02 are linked to lead01). The only way to get a working criterion is to know and paste the record's UUID. Server logic is correct when the UUID is sent (API): equals X -&gt; R01,R02; not_eq… | Defect: Lookup criterion value is a plain text box - no record picker, so 'equals &lt;record&gt;' cannot be built in the UI</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. Second user = ALT1 (Mahmoud Mohamed, Admin profile) - test user 1 (User profile) credentials were not available; $me resolution does not depend on profile. Seeds (FieldPermissions): R01-R05 owned by OWNER, R06-R10 reassigned to ALT1. As OWNER, 'QA CV owner-me' built in the editor: Name starts with 'QA CV' + Owner equals 'Current user' (picker option), shared with Everyone -&gt; POST value '$me', visibility everyone; grid 5 records. Grid call (records?view_id) as OWNER -&gt; R01..R05; as ALT1 -&gt; R06..R10. Module filter owner = own user id with each user's token gives the same sets. ALT1 GET view: cat…</t>
-  </si>
-  <si>
-    <t>L01 and L02 selected in the grid -&gt; Module actions -&gt; Manage Tags; tag 'QA CV VIP' created via 'New tag' (typing a new name in the Tags box and pressing Enter does not create it) and applied -&gt; 'Tagged 2 records.'. View 'QA CV tags' (Full Name starts with 'QA CV' + Tags Contains any of QA CV VIP) saved from the editor: grid 2 records = QA CV L01, L02; API filter total 2, same records. Tags operat…</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Failed (Medium). First pass was a false positive: every POST used pattern '(1)' with one row, and the API rejects that for the pattern alone ('A pattern needs at least two criteria rows'). Re-run with valid patterns (control view with 1 row + pattern null -&gt; 201): unknown field does_not_exist_c -&gt; 422 unknown_field 'That field does not exist on this module.' (1 and 2 rows); unknown operator xor_like -&gt; 422 "filters[n].operator 'xor_like' is not a supported operator."; PATCH with the unknown field -&gt; 422, view unchanged. FAIL: Deals 'QA CV wrong-type' with Amount (currency) + operator contains -&gt; 201 Created (a… | Defect: API stores a criteria operator that is invalid for the field type (contains on a currency field)</t>
-  </si>
-  <si>
-    <t>Run 2026-10-04 (execu_2026-10-04_17-47-37): Passed. 'QA CV and-default' built in the editor with 3 rows (Full Name starts with 'QA CV L0'; Lead Status is not empty; Comment is empty), pattern untouched - POST sends pattern null. Reopened editor shows AND between rows and 'Criteria Pattern ( 1 and 2 and 3 )'. Grid: 6 records L01, L02, L05, L06, L07, L08 (L03/L09 have whitespace-only Comment, L04 'Call back'); module filter with the 3 conditions ANDed returns the same 6.</t>
-  </si>
-  <si>
-    <t>Rows: 1 Lead Status equals No Answer, 2 Lead Status equals Busy, 3 Comment is not empty (QA CV L01 given a comment). Pattern entered '(1 or 2) and 3' -&gt; shown as '( (1 or 2) and 3 )', stored settings.criteria.pattern '(1 or 2) and 3'. Reopened editor shows the same; saving again without changes -&gt; PATCH 200, pattern unchanged. Grid before and after: 2 records (QA CV L01, AEX-01). Cross-check: (No…</t>
-  </si>
-  <si>
-    <t>Arabic UI: the criteria pattern '(1 or 2) and (3 or 4)' is displayed as '( and (3 or 4) (or 2 1) )' - brackets and order reversed</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-D24-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>Last Activity' in view criteria is the record's modified time; adding a note does not update it (NDC-1868 P1-5 expects activity time)</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-D25-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>Contacts link fields from Deals: Contact, Connected To, Lookup ('Lookup 2' in the case does not exist; 'Lookup' used). Seeds: C01 &lt;- D01 via Connected To, C02 &lt;- D03 via Lookup, both deals Stage negotiation (Stage is labelled 'Test-Stage' on this tenant). View 'QA CV link-field' (First name starts with 'QA CV' + with Deals, Test-Stage equals negotiation) saved from the editor. Any link field -&gt; C…</t>
-  </si>
-  <si>
-    <t>Contacts editor: related blocks Deals, Tasks, Calls added and saved ('QA CV related-limit', 201). 'Add condition' then disabled with title 'A view can use at most 3 related modules.'. API POST with a 4th related_criteria entry -&gt; 422 settings.related_criteria too_many 'A view may use at most 3 related modules.'; no view created. Grid count 0 = API view count 0.</t>
-  </si>
-  <si>
-    <t>Deals block rows: Test-Stage equals negotiation, Amount greater than 0, Deal name starts with 'QA CV' -&gt; saved ('QA CV block-rows', 201); 'Add criteria row' in the block disabled with 'A maximum of 3 criteria rows is allowed'. Results: QA CV C02 only (D03 negotiation, amount 10000; D01 amount 0 excluded) - grid 1 record = API 1. API POST with 4 rows in the block -&gt; 422 related_criteria[0].criteri…</t>
-  </si>
-  <si>
-    <t>Module with no related modules: the editor still shows an empty related block and an enabled 'Add condition' (module list empty)</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-E07-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>Six rows 'Account (Accounts) › Created Time · Is not empty' -&gt; Save blocked: 'At most 5 criteria rows can use fields of lookup modules. Remove the highlighted rows.' (a generic 'Complete this row…' alert appeared too). With 5 rows -&gt; saved ('QA CV lookup-path', stored field account_id.accounts.created_at). API POST with 6 lookup rows -&gt; 422 too_many_lookup_fields 'At most 5 criteria rows may use …</t>
-  </si>
-  <si>
-    <t>List preferences accept more than 50 column overrides (51 stored); no oldest-dropped or 4xx rule</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-F04-51-overrides.json</t>
-  </si>
-  <si>
-    <t>Toolbar sort label shows API names ('Sort: amount desc') instead of field label and direction</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-F06-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>All Leads at 25 rows per page (1–25 of 106). Header checkbox selected every selectable row on page 1: 20 selected, bar '20 selected'; the other 5 rows are 'Awaiting approval — locked' records, which have no checkbox. Page 2: 0 rows ticked (the bar still shows the page-1 count). Back on page 1, unticking cleared all rows and the bar. Page size set back to 10 afterwards.</t>
-  </si>
-  <si>
-    <t>View 'QA CV select' (Full Name starts with 'QA CV L'): L01, L02, L03 selected, bar '3 selected'. Switched to All Leads: no rows selected, no bar. Switched back to 'QA CV select': no rows selected, no bar.</t>
-  </si>
-  <si>
-    <t>View 'QA CV export' (Full Name starts with 'QA CV L'; columns Full Name, Lead Status, Company) - 14 records. Module actions -&gt; Export Leads dialog: 'All records (14)' / 'Current page only', 'Visible columns (4) - the columns shown in the table, in the same order, plus Tags' / 'All fields'. Exported with defaults -&gt; leads-export-2026-10-04.xlsx, toast 'Export downloaded'. File: 14 data rows = exac…</t>
-  </si>
-  <si>
-    <t>View 'QA CV empty' (Full Name equals 'QA CV no-such-record') saved from the editor. Opened: '0 records' and 'No results' empty state; no alert/toast, no API 4xx/5xx, no console error. Records filter API total 0.</t>
-  </si>
-  <si>
-    <t>Dropdown picker: "Clone" and "Delete view" in a view menu do nothing (no request, no dialog); they work from the tab menu</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-G04-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>16th pin accepted (204) and stored; picker silently shows only 15 - pin limit not enforced</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-G06-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>"QA CV restore-me" (criteria, 3 columns, sort first_name asc, page size 25, visibility everyone) saved via API, row_version 1. Deleted from the tab menu: dialog "Delete custom view? … It moves to the Recycle Bin; its records are not affected." -&gt; "\"QA CV restore-me\" was deleted.", GET 404. Settings › Recycle Bin listed it (CRM Saved View, expires in 60 days); Restore -&gt; "Restore 1 item?" -&gt; res…</t>
-  </si>
-  <si>
-    <t>Selected "QA CV last-used" in Leads (lastListViewId = its id). Opened Deals; DELETE the view via API (204). Opened Leads: All Leads selected, no error page, no toast, no failed API call or console error; "QA CV last-used" not in the tabs or the picker.</t>
-  </si>
-  <si>
-    <t>Contacts has 0 Kanban views. Clicking 'Kanban view' opens the 'New Kanban view' settings form directly (Name, Categorize by, Aggregate by, Header style, Select fields, Share with); Cancel returns to the list. The board never shows the 'No Kanban views yet' empty state the case describes - but Zoho behaves the same way (clicking Kanban on Contacts with no Kanban views opens 'Kanban View - Settings…</t>
-  </si>
-  <si>
-    <t>Leads › Kanban › new Kanban view › Categorize by offers: Lead Status (status), Reason (pick list), Lead Source (pick list), Complaint Reason (pick list). Compared with the Standard layout's fields (single line, email, phone, multi line, URL, user, date-time, pick list, status): no multi-select, text, number, date or lookup field is offered. Form hint: 'Single-value pick list, status or radio-butt…</t>
-  </si>
-  <si>
-    <t>No module on NDC-Staging lacks a groupable field (Leads 63, Contacts 3, Deals 5, Accounts 5, Tasks 4, Calls 6, Meetings 4, Subscriptions 4, test 2). Created custom module 'QA CV No Picklist' (API, text fields only): it still gets a system 'Approval Status' pick list, which the Kanban form offers under Categorize by and allows saving with. So a module without a pick list/status/radio field cannot …</t>
-  </si>
-  <si>
-    <t>New Kanban view on Leads: 3 card fields selected by default (Full Name, Phone, Email). Added up to 10; the Standard layout only has 10 card-able fields, so after 10 the Available list is empty (no 11th to add in the UI). API PATCH with 11 card_fields -&gt; 422 settings.card_fields too_many 'A card can show at most 10 fields.'; stored stays 10. Move up/down reorders (Complaint Reason moved up 2); sav…</t>
-  </si>
-  <si>
-    <t>Kanban view 'QA CV kb-status' (Lead Status). Edit -&gt; Header style Mono color -&gt; Save -&gt; after reload every column header uses the same blue top bar. Edit -&gt; Multi color -&gt; Save -&gt; after reload each column has its own colour (No Answer blue, Busy green, Switched Off orange, Wrong Number purple, …). Stored settings.header_style follows (multi at the end).</t>
-  </si>
-  <si>
-    <t>QA CV kb-edit' categorized by Lead Status: 16 status columns + Unaccounted. Edited Categorize by -&gt; Lead Source, saved: board rebuilt with chat, web, referral, other + Unaccounted (= the 4 Lead Source values); GET settings.categorize_field = lead_source.</t>
-  </si>
-  <si>
-    <t>Choose a Kanban view -&gt; Manage Kanban views opens a 'Manage Kanban Views' dialog listing QA CV card-fields, QA CV kb-edit, QA CV kb-status, test (columns View name, Used field, Layout, Shared to, Last modified by, Created by, Actions) - the same 4 names GET ?kind=kanban returns. 'Create Kanban View' opens the Kanban settings form; closed without saving.</t>
-  </si>
-  <si>
-    <t>Kanban column cap: records whose value is past the 75th are hidden (no 'Other values' column) and board-summary says truncated=false</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-H14-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>Kanban: a record holding a removed pick-list value is shown in a normal-looking column with no 'no longer an option' flag</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-I04-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>Network throttled through the browser's DevTools protocol (2 s latency, 50 KB/s), board 'QA CV kb-status' reloaded. Cards first became visible after 46 s; QA CV L05 dragged to Follow Up at that moment: no PATCH, no toast, no 'The board is still loading — try again in a moment.' message; after removing throttling L05 is still Interested. A state where cards are draggable while the board is still l…</t>
-  </si>
-  <si>
-    <t>Board 'QA CV kb-status': QA CV L07 (Interested) dragged ~50 px and dropped back inside Interested. No PATCH/PUT/POST on records was sent; Interested count stayed 13. (No write, so no history entry.)</t>
-  </si>
-  <si>
-    <t>QA CV L08 card (role=button, aria-roledescription=draggable) focused; Enter picks it up, ArrowRight -&gt; live region 'is over Follow Up', Enter drops -&gt; 'Dropped … into Follow Up.', PATCH 200, toast 'Record updated successfully', API lead_status = Follow Up - same save path as a mouse drag. The keyboard model is pick-up/arrow/drop (no move menu). The 'move to Unaccounted is refused' half could not …</t>
-  </si>
-  <si>
-    <t>Interested: Collapse column -&gt; collapsed (button becomes 'Expand column'), Expand -&gt; expanded. 'Collapse all columns' -&gt; all 17 collapsed; 'Expand all columns' -&gt; all 17 expanded. Follow Up collapsed; QA CV L09 dragged onto the collapsed Follow Up -&gt; PATCH 200; after expanding, L09 is in Follow Up; counts Interested 13-&gt;12, Follow Up 2-&gt;3; API lead_status = Follow Up.</t>
-  </si>
-  <si>
-    <t>Deals Kanban 'QA CV deals-by-stage' (Stage, aggregate Amount; board layout picker Standard). The 'Create Deal' link in the negotiation column footer opens /records/new?layout=fcba0068…&amp;prefill_field=stage&amp;prefill_value=negotiation with Stage = negotiation, Pipeline = Standard, layout Standard. Saved 'QA CV D09' -&gt; 201; API stage negotiation, pipeline 5170500c… (Standard), created_with_layout fcba…</t>
-  </si>
-  <si>
-    <t>Interested had 13 cards loaded. Column checkbox 'Select all loaded records in Interested' -&gt; bulk bar '13 selected'; only Interested cards checked; unticking cleared the bar. No bulk action run. Accessibility issue found (recorded under L05): every card's checkbox has the same accessible name as the column's select-all ('Select all loaded records in &lt;column&gt;').</t>
-  </si>
-  <si>
-    <t>Board 'QA CV kb-status' open (Interested 11, Follow Up 4). QA CV L10 changed to Follow Up from outside the board (API PATCH 200). Without a reload the headers updated after 21 s: Interested 10, Follow Up 5.</t>
-  </si>
-  <si>
-    <t>Contacts has no split views. 'Split view' opens the 'Create Split View' form directly (Name, View based on Picklist/User or Criteria, Split by, Splits - 'The selection is limited to a maximum of 10 values.', Select columns); Cancel closes it. No 'No split views yet' empty state is shown - Zoho does the same (Split View on Contacts goes straight to /split-views/create), so the result matches the r…</t>
-  </si>
-  <si>
-    <t>Leads › Create Split View, View based on Criteria, New Split: criteria rows added one by one; at 10 rows 'Add criteria row' is disabled with title 'A maximum of 10 criteria rows is allowed'. Picklist/User mode states 'The selection is limited to a maximum of 10 values.' (the value chooser could not be driven by automation, so values were checked through the API). API: one split with 11 criteria -…</t>
-  </si>
-  <si>
-    <t>Split view 'QA CV split-status' (Lead Status: Busy, Interested, Follow Up), Records per split = 10: Busy (16) shows 10 rows, Interested (10) 10, Follow Up (5) 5. 'Create Lead' in the Interested section opens /records/new?…&amp;prefill_field=lead_status&amp;prefill_value=Interested with Lead Status = Interested. Saved 'QA CV L15' (phone in local format; '+20…' was refused 'This value does not match the re…</t>
-  </si>
-  <si>
-    <t>Arabic UI: header layout picker accessible name and the 'records' count text are not translated</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-L03-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>Keyboard: focus lost to page body after 'Add criteria row' and pattern Save; view picker menu has no arrow-key navigation</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-L04-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>Kanban accessible names: card checkboxes reuse the column 'Select all loaded records in …' name, column buttons lack the column name, drag announcements read UUIDs</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-L05-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>At 390 px the Leads list header breaks: empty tab column, view picker button covered by Filter (cannot be tapped), Create Lead cut off</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-L06-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>Firefox: React ErrorBoundary console error (lazy-loaded component) during the view/Kanban flow</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-L07-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>List first page p95 6.8 s (Leads) / 3.9 s (Deals) vs 1.5 s target</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-L08-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>Kanban headers + first cards p95 10.2 s vs 2 s target; '0 records' shown while loading</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-04_12-29-38/bugs/screenshots/cv-122938-874a-L09-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>16 pinned + 50 'QA CV perf-NN' views created via API (169 list views in the tenant, 165 picker items). Picker open timed in-page (press -&gt; search box + item list stable for 2 frames), 10 times: 345, 239, 236, 258, 215, 233, 220, 243, 265, 221 ms (max 345 &lt; 500). Search 'perf-4' -&gt; list shows only perf-40..49 in 25 ms; 'zzz' -&gt; 'No views match.' in 12 ms. Step 4 (unpin all) done in cleanup.</t>
-  </si>
-  <si>
-    <t>List view 'QA CV عملاء' (this run's own view from B, criterion added: Full Name contains 'أحمد') and Leads Kanban 'QA CV لوحة' (Lead Status) - both set up through the API, then checked in the Arabic UI (dir=rtl). Overflow picker search 'عملاء' lists 'QA CV عملاء'; tab shows 'QA CV عملاء'; Manage custom views row 'QA CV عملاء' (rtl); editor title 'تعديل طريقة العرض المخصصة: QA CV عملاء', criterion…</t>
-  </si>
-  <si>
     <t>Sources: Low/Medium = run execu_2026-10-04_12-29-38; High/Urgent = run execu_2026-10-04_17-47-37. Missing = case marked Missing in the Test Cases sheet.</t>
   </si>
   <si>
-    <t>execu_2026-10-05_10-50-12 (A03/A04 rerun as test user 1)</t>
-  </si>
-  <si>
-    <t>A User-profile user (no Manage Shared Views) can create public views through the API (POST 201, visible to everyone under Public views). Was Inconclusive in execu_2026-10-04_17-47-37 (no User-profile login).</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-05_10-50-12/bugs/screenshots/a03-a04-105012-9ff8-A03-vs-zoho.png</t>
-  </si>
-  <si>
-    <t>A user a view is shared with can edit and delete it (can_edit/can_delete true, PATCH 200, DELETE 204); the deleted view bypasses the Recycle Bin. Was Inconclusive in execu_2026-10-04_17-47-37 (no User-profile login).</t>
-  </si>
-  <si>
-    <t>executions/execu_2026-10-05_10-50-12/bugs/screenshots/a03-a04-105012-9ff8-A04-vs-zoho.png</t>
+    <t>execu_2026-10-05_11-20-40 (staging-crm.taviportal.com)</t>
+  </si>
+  <si>
+    <t>Leads as Owner: List/Kanban/Split view switchers present; picker ('Custom views' in dropdown mode) with Search views and footer New custom view, Manage custom views, Show custom views as tabs. Switched to tabs: tab list 'Custom views' with test, All Leads, Recently Created/Modified Leads, Today's Leads, My Leads; overflow 'More custom views' with the same footer.</t>
+  </si>
+  <si>
+    <t>GET views?kind=list with bearer + x-tenant-id: 200, 7 views. Without x-tenant-id: 200, identical 7 views. With another tenant id (…0003) or a non-UUID value: 200, the same NDC-Staging views. Recorded behaviour: the header is ignored and the tenant comes from the session; no request returned another tenant's data.</t>
+  </si>
+  <si>
+    <t>/views/{All Leads}/edit: name shown as locked text 'All Leads' with 'System-defined views keep their name and criteria. You can change their columns, sort and page size.'; no name input and no criteria section (cannot be changed); columns (Add field), Sort by, Direction and Records per page enabled; Save enabled. Note: the criteria section is hidden rather than shown read-only.</t>
+  </si>
+  <si>
+    <t>Still no way to turn custom views off in CRM: this build loads the same featureFlags-Bty4zi8j.js, whose four flags are all hard-coded to return true. No workspace with custom views turned off exists, so the message cannot be reached.</t>
+  </si>
+  <si>
+    <t>As test user 2 (profile 'test', no metadata.views.manage): New custom view 'QA CV private' - Share with offers only 'Only me' with 'You need the Manage Shared Views permission to share a view with other people.'; Save -&gt; 201, stored visibility private; picker shows it under CREATED BY ME. Note: Everyone / Selected users are hidden rather than shown disabled. Deleted afterwards.</t>
+  </si>
+  <si>
+    <t>As test user 2 (no metadata.views.manage): POST views {kind:list, name:QA CV api-public, visibility:everyone} -&gt; 403 PERMISSION_DENIED; with a complete body -&gt; 403; not in the user's list nor the Owner's list. (Yesterday's Fail used test user 1, whose User profile includes metadata.views.manage, so that result did not test this case.)</t>
+  </si>
+  <si>
+    <t>Owner shared 'QA CV shared' with test user 2 only. As test user 2: GET -&gt; can_edit=false, can_delete=false; /edit shows 'You cannot edit this view - Only its owner, or someone who can manage shared views, can change it.' with no Save; PATCH name -&gt; 403 PERMISSION_DENIED; DELETE -&gt; 403. Owner re-reads: name 'QA CV shared', row_version 1 (unchanged). (Yesterday's Fail used test user 1, who has metadata.views.manage.)</t>
+  </si>
+  <si>
+    <t>As test user 2: GET Owner's private view by ID -&gt; 404 NOT_FOUND, no name or criteria in the body; /edit shows 'View not found - This view was deleted, or it is not shared with you.'; /modules/{Leads}?view={id} shows no part of the view (picker shows 'Choose a view').</t>
+  </si>
+  <si>
+    <t>QA CV selected' shared with test user 2 only. Outsider test user 1 (no Manager-profile account exists; test user 1 is not in the share list): picker search -&gt; 'No views match.', list API does not contain it, GET by ID -&gt; 404 NOT_FOUND with no name. Test user 2 sees it under SHARED WITH ME.</t>
+  </si>
+  <si>
+    <t>As test user 2 on All Leads: Manage columns -&gt; Apply shows 'You changed the columns for this view. Only you see this change.'; no 'Save to view' offered; the user's list-preferences hold a personal viewColumns entry for All Leads; the view itself is unchanged (row_version 3 before and after, 7 columns; Owner sees the same). Note: Company was not in test user 2's column panel (7 visible columns only), so the change applied was the column set itself.</t>
+  </si>
+  <si>
+    <t>Needs a user whose profile lacks metadata.records.manage. Both available lower-profile accounts have it (test user 1 'User': metadata.records.manage true; test user 2 'test': true), so the precondition cannot be met.</t>
+  </si>
+  <si>
+    <t>Needs a signed-in user of another tenant. The case points to Test Data/AnywareStagingTempAccounts.txt; that credentials file was not used without the tester's go-ahead (credentials are only used from paths the tester gives).</t>
+  </si>
+  <si>
+    <t>Picker search: 'Search' -&gt; QA CV Search Alpha and QA CV Search Public; 'qa cv search alpha' -&gt; QA CV Search Alpha; 'عملاء' -&gt; QA CV عملاء; 'zzqq-no-match' -&gt; 'No views match.'; cleared -&gt; all 18 entries back.</t>
+  </si>
+  <si>
+    <t>Ticked QA CV tab1 and tab2, unticked Today's Leads. Tab bar before and after reload: test, All Leads, Recently Created Leads, Recently Modified Leads, My Leads, QA CV tab1, QA CV tab2; openListViewIds holds exactly these 7 IDs and all resolve (no deleted IDs - yesterday's stale-ID failure is not reproduced). Observation: My Leads (8f163184) is in both openListViewIds and recentlyClosedListViewIds.</t>
+  </si>
+  <si>
+    <t>Tab menu on QA CV pinned: Edit, Pin view, Clone, Close view, Delete view. After Pin view, both 'Show as tab: QA CV pinned' checkboxes are disabled and ticked with the title 'Pinned views always show as tabs. Unpin the view to hide its tab.'; a forced click leaves it ticked; the tab stays. Observation: the message is only a native title (no aria-describedby, not shown as text).</t>
+  </si>
+  <si>
+    <t>Show custom views as a dropdown' -&gt; after reload a 'Custom views' dropdown, no tab list (pref listPickerMode=dropdown); 'Show custom views as tabs' -&gt; after reload the tab list with 8 tabs (pref=tabs).</t>
+  </si>
+  <si>
+    <t>All Leads 'Actions' menu: Edit columns, Pin view, Clone (disabled, title 'You cannot clone a system-defined view.'), Close view. No Delete view and no rename. Note: the expected list's 'Delete View' conflicts with its own 'Delete view ... not offered'; Delete is not offered.</t>
+  </si>
+  <si>
+    <t>Leads: selected QA CV x -&gt; Deals shows All Deals -&gt; Leads still QA CV x -&gt; Deals still All Deals. list-preferences: Leads lastListViewId = QA CV x, Deals lastListViewId = All Deals (9707b09e).</t>
+  </si>
+  <si>
+    <t>Run as test user 2 with no other sign-in of that user during the wait. Request 1 without Authorization -&gt; 401 TOKEN_MISSING 'Authorization token is required.', no view data. Token issued 08:57:23Z, exp 09:02:23Z (5 min): at 09:01:54 (before expiry) -&gt; 200 with views; at 09:03:42 (80 s after expiry, &gt;6 min after issue) -&gt; 401, no view data. Note: the code is SESSION_REVOKED ('This session has been revoked.') rather than an expiry-specific code. (Two earlier attempts were invalid: one was revoked by a server-wide revocation around 08:30, the other by this run's own sign-in of the same user.)</t>
+  </si>
+  <si>
+    <t>11 'QA CV close' views shown as tabs. Close view on close01 -&gt; Recently closed: QA CV close01, Today's Leads*, My Leads*. After closing close02…close11 -&gt; Recently closed shows exactly 10: close11 … close02 (close01 dropped); recentlyClosedListViewIds holds the same 10 in the same order; no close tabs left.</t>
+  </si>
+  <si>
+    <t>Leads, Deals, Contacts, Tasks and Subscriptions each have 5 system views (keys all, my, recently_created, recently_modified, today). All returns everything (Leads 10730); My only the viewer's (owner criterion $me; Deals/Tasks pages all owner; Leads Standard layout 49/49 owner); Recently Created sorted by created_at desc, Recently Modified by updated_at desc; Today's only records created today in Cairo time (Leads 21/21). Note: on the Leads 'New Layout' layout the Owner field is not on the layout, so the API omits it from those records.</t>
+  </si>
+  <si>
+    <t>QA CV L01 owned by OWNER, QA CV L02 owned by test user 2 (USER). OWNER's My Leads (Standard layout): 49 rows, all owned by OWNER, includes L01, not L02. Test user 2's My Leads: 3 rows, all owned by test user 2, QA CV rows = L02 only.</t>
+  </si>
+  <si>
+    <t>Needs leads created at 23:50 Cairo on D-1 and 00:10 Cairo on D; created_at cannot be backdated, and no existing lead falls in either window (Today's Leads: 21 records, oldest created 06:22 UTC today). Supporting check: Today's views in 5 modules return only records created today in Cairo time (B07). To settle it, create the two leads around 21:00 UTC (midnight Cairo).</t>
+  </si>
+  <si>
+    <t>QA CV x (101 records, 10 per page). Sort dialog: Created At + Descending -&gt; Apply ('Sort: created_at desc'); Next page -&gt; page 2. Opened the 3rd record, browser Back -&gt; QA CV x, Sort: created_at desc, page 2, same first row. Opened it again, in-app Back -&gt; same view, sort and page 2. Note: the sort label shows the API names (see F06).</t>
+  </si>
+  <si>
+    <t>Selected QA CV x; list-preferences lastListViewId = QA CV x (fd6535d1). Profile drawer -&gt; Logout; signed in again; Leads opens with QA CV x selected.</t>
+  </si>
+  <si>
+    <t>?view= with a deleted or foreign view ID falls back to the last-used view instead of All Leads - ?view= own QA CV x -&gt; opens; QA CV shared-to-me (shared by test user 1) -&gt; opens; deleted QA CV gone and test user 1's private QA CV user-private -&gt; toast 'That view is no longer available. Showing your default view.', ?view= removed, nothing of the foreign view shown, no console errors. FAIL: the fallback is not All Leads - both land on the last-used view (QA CV close11).</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-B14-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>List preferences changed in two browser tabs: the later write silently overwrites the earlier one (lost update, no version conflict) - QA CV A and QA CV B shown as tabs. Tab 1 selected A, tab 2 selected B. Tab 1 closed B (its tab bar: A). Tab 2 (stale) closed A (its tab bar: B). Final list-preferences (version 193): openListViewIds has B and not A; recentlyClosedListViewIds starts with A and does not contain B; after reloading tab 1 the B tab is back. Lost update: tab 2's write replaced the whole preference object and undid tab 1's close; no conflict was raised.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-B15-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>New custom view 'QA CV no-criteria' with no criteria -&gt; 201, category created_by_me; returns 101 records on the Standard layout, the same as All Leads (101).</t>
+  </si>
+  <si>
+    <t>View name validation messages are never shown: empty/space-only names just disable Save, and a 121-character name is silently cut to 120 - D1 '' and D2 ' ': Save is disabled and 'Enter a name for the view.' is never shown. D5 (121 chars): the input stops at 120 characters, so 'A view name can be at most 120 characters.' never appears (the truncated name then hit 409 VIEW_NAME_TAKEN against the D4 view). D3 'Q', D4 (120), D8 Arabic, D9 (RLM kept), D10 emoji saved exactly as typed. D6 stored trimmed ('QA CV trim'). D7 'qa cv NAME' refused as a duplicate of 'QA CV name' (409, names are case-insensitive). D14 zero-width space and U+0007 kept as typed. D11 '&lt;img src=x onerror=alert(1)&gt;' shown as literal text in the tab, picker, Manage page and delete dialog; no &lt;img&gt; element, no script ran.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-C02-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>OWNER already owns 'QA CV dup'. New custom view 'QA CV dup' -&gt; Save refused, 409 VIEW_NAME_TAKEN, message 'You already have a view with this name.'; only one 'QA CV dup' (owner), row_version 1 unchanged.</t>
+  </si>
+  <si>
+    <t>As test user 2 (lower profile), New custom view 'QA CV dup' -&gt; 201, toast 'Custom view "QA CV dup" created.', listed under test user 2's CREATED BY ME. OWNER's 'QA CV dup' unchanged.</t>
+  </si>
+  <si>
+    <t>Rule recorded: names are unique per owner and per kind. As OWNER the queue POST cannot reach the name check (409 WORKQUEUE_LIMIT - the owner already owns 15 queues). As test user 1: list 'QA CV k' -&gt; 201 and queue 'QA CV k' -&gt; 201; GET ?kind=list returns only the list, ?kind=queue only the queue.</t>
+  </si>
+  <si>
+    <t>Row Company | Contains | (empty), name 'QA CV incomplete' -&gt; Save blocked with 'Complete this row (field, operator and value) or remove it.'; no POST sent; no 'QA CV incomplete' exists.</t>
+  </si>
+  <si>
+    <t>QA CV partial' with 2 criteria rows, 8 columns, sort created_at asc, page size 50. PATCH {name:'QA CV partial-2', row_version} -&gt; 200. Changed fields: only name, row_version and last_modified_at; settings, visibility and shared_user_ids identical.</t>
+  </si>
+  <si>
+    <t>PATCH is_system:true / owner_user_id:&lt;test user 2&gt; / category:public_views + can_edit:false / row_version:999 -&gt; each 200 with the key ignored: is_system false, owner unchanged, category created_by_me, can_edit true; row_version only advanced +1 per save (1 -&gt; 5). A PATCH with expected_row_version 1 -&gt; 409 VERSION_CONFLICT 'The view changed since you loaded it (current version 5).'</t>
+  </si>
+  <si>
+    <t>name 12345 / ['QA CV arr'] / {x:1} -&gt; 400; name null -&gt; 422; columns 'name' / {a:1} -&gt; 422; criteria 'status=1' / [] / 7 -&gt; 422; page_size '25' / [25] / {n:25} -&gt; 422; no 500, list count unchanged. columns:null and page_size:null -&gt; 201 (valid 'not set' values per the contract; deleted again).</t>
+  </si>
+  <si>
+    <t>Run as test user 1. Editor filled ('QA CV expiry', Full Name Is not empty, columns) at 09:13:27 and left open; the app refreshed the token in the background (POST /iam/auth/refresh 200 at 09:17:26). Save at 09:19:07 -&gt; 201 at 09:19:18 (11 s); stored 1 condition; name still filled before save. No data lost. Observation: the save took 11 s with the editor still showing.</t>
+  </si>
+  <si>
+    <t>Editor: 25 rows (Full Name Is not empty) added; 'Add criteria row' is disabled at 25; the 25-row view saved (201) with 25 stored conditions. API: POST with 26 conditions -&gt; 422 INVALID_VIEW 'At most 25 criteria rows are allowed.'; no 'QA CV 26-rows' exists. Note: the disabled add button has no tooltip explaining the limit.</t>
+  </si>
+  <si>
+    <t>Editor shows 'No columns chosen: everyone sees their usual columns.'; 'QA CV no-columns' saved (201). Its grid shows the owner's usual columns (list-preferences visibleKeys: Full Name, Phone, Lead Status, Lead Owner, Created At, Last Activity) plus Tags and Source.</t>
+  </si>
+  <si>
+    <t>Editor (FieldPermissions layout): no tip at 10 columns; at 11 'Tip: more than 10 columns makes the table hard to read.'. API: a 30-column view saves (201); PATCH with 31 columns -&gt; 422 INVALID_VIEW 'A view may show at most 30 columns.'; GET still shows 30. Note: the 30-column save from the editor itself was interrupted by an owner-session revocation, so the 30-column save was confirmed through the API.</t>
+  </si>
+  <si>
+    <t>Page size 200 is accepted by the server but cannot be chosen in the editor; with 200 stored the editor shows 'Select…' and the grid's Rows per page reads 10 - Works: 'QA CV sort-page' sorted Created At descending (header 'Created At ↓') with page size 10; PATCH page_size 9 and 201 -&gt; 422 'Page size must be a whole number between 10 and 200.', stored value unchanged. FAIL: the editor offers only Each person's usual page size / 10 / 25 / 50 / 100 - 200 cannot be chosen although the server accepts it (PATCH 200 -&gt; 200). With 200 stored, the editor shows 'Select…' and the grid shows 1–101 of 101 rows while its Rows per page control reads 10.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-C12-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Run as ALT1 (Admin; owner sessions were being revoked by another sign-in). 'QA CV no-users', Share with = Selected users, no user picked, Save -&gt; blocked with 'Choose at least one user, or share with everyone instead.'; no view created. API: POST visibility 'selected' with shared_user_ids [] -&gt; 422 INVALID_VIEW 'Select at least one user to share this view with, or choose a different visibility.'</t>
+  </si>
+  <si>
+    <t>Run as ALT1. Filled name 'QA CV discard', a criteria row; Cancel -&gt; back to Leads, no POST; repeated with the top Back control -&gt; back to Leads, no POST. List count unchanged; no 'QA CV discard' exists. (No 'discard changes?' prompt - not required.)</t>
+  </si>
+  <si>
+    <t>UI (ALT1): double-click Save on 'QA CV double' sent one POST (201); one view exists - the Save button now guards against the second click. API (OWNER): two parallel POSTs 'QA CV double-api' -&gt; 201 and 409 VIEW_NAME_TAKEN; one view exists.</t>
+  </si>
+  <si>
+    <t>A view's grid shows two columns that were not chosen (Tags and Source are always appended) - Run as ALT1. Editor (Standard layout): added Full Name, Lead Status, Company, Email, Phone, Lead Owner, Created At, Last Activity in that order ('Modified Time' is not offered; Last Activity = last_modified_at). Saved (201); stored columns in exactly that order. Grid after selecting the view: Full Name, Lead Status, Company, Email, Phone, Lead Owner, Created At, Last Activity - order correct - but two unchosen columns, Tags and Source, are appended.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-C09-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Run as ALT1. 'QA CV conflict' opened in the editor in two browser tabs. Tab 1 renamed to 'QA CV conflict-1' and saved (PATCH 200). Tab 2 changed the criteria value and saved -&gt; 409 VERSION_CONFLICT; tab 2 shows 'Someone else saved this view after you opened it. Reload to get the latest version — your unsaved changes will be lost.' with Reload; after Reload the name is 'QA CV conflict-1'. Final view: name QA CV conflict-1, criteria value unchanged (tab 2's change not saved), row_version 2.</t>
+  </si>
+  <si>
+    <t>Run as ALT1 on layout 'New Layout' (Standard has no checkbox field): rows Single Line Is empty, Created At Today, Use Wallet Number Is true. No value input appeared for any row; Save -&gt; 201; stored conditions single_line is_empty null, created_at today null, use_wallet_number is_true null. Results: QA CV N01 (created today, wallet true, single line empty) only; the other 7 wallet-true records on the layout are excluded (not created today). Note: the Created Time field is labelled 'Created At' in the editor.</t>
+  </si>
+  <si>
+    <t>Run as ALT1. Editor on Standard shows 'Applies to the "Standard" layout — its fields and its records.'; 'QA CV layout' saved with layout Standard. Views API lists it for layout Standard, not for New Layout. Picker on New Layout: 'No views match.'; back on Standard it is listed under CREATED BY ME and returns 101 records. Observation: GET records?view_id=&lt;it&gt;&amp;layout_id=&lt;New Layout&gt; is not refused (returns 14 records), but the UI never makes that call.</t>
+  </si>
+  <si>
+    <t>ALT1 created 'QA CV shared15' (Full Name starts with 'QA CV L' + Lead Status equals 'No Answer' = status of L01), shared with test user 2 only. Test user 2's grid: L01, L15. ALT1 changed the criterion to 'Busy' (status of L02) -&gt; 200. Test user 2 reloads the view: L02, L13, L14 (3 records) - matches the new criterion. Note: the deep-linked grid can take more than 8 s to load (see L08).</t>
+  </si>
+  <si>
+    <t>Run as ALT1. Filter sidebar: Lead Status, operator Equals, Busy ticked, Apply Filter -&gt; 18 records (URL f=[{fieldKey:lead_status, operator:equals, value:Busy}]). New custom view shows 'The criteria start with the filters applied on the records page.' with the row 'Leads | Lead Status | Equals | Busy'. Saved 'QA CV from-filter-3': stored criteria lead_status equals Busy; the view returns the same 18 records. Observation: after saving, the list filter stays in the URL (&amp;f=…) on top of the new view.</t>
+  </si>
+  <si>
+    <t>As ALT1: created 'QA CV audit', edited its criteria, shared it with Everyone, cloned it, deleted the clone. Audit Log (Settings &gt; Security &gt; Audit Log, API /audit/events) has 5 entries, each with actor 'Mahmoud Mohamed' (ALT1) and time: 10:13:02 created 'QA CV audit', 10:13:02 updated, 10:13:03 updated (sharing), 10:13:03 created 'Copy of QA CV audit' (clone), 10:13:03 deleted 'Copy of QA CV audit' (app metadata-engine, entity module_view). Note: the sharing change and the clone are logged as generic updated / created entries.</t>
+  </si>
+  <si>
+    <t>Run as ALT1. Editor operator lists: Text (Company) = Contains, Does not contain, Equals, Not equal to, Starts with, Ends with, Is empty, Is not empty. Number/Currency/Amount = Equals, Not equal to, Greater than, Less than, ≥, ≤, Is empty, Is not empty (no between). Date = Is, Is before, Is after, Is between, Is not between, Today, Yesterday, Tomorrow, This/Last/Next week, month, year, In the last/next N days, Age in days, Due in days, Before now, After now, Is empty, Is not empty. Date-time = the date set plus In the last/next N hours. Checkbox = Is true, Is false. Pick list / status / Source / Stage = Contains any of, Contains none of, Equals, Not equal to, Is empty, Is not empty. Multi-select and Tags = Contains any of, Contains all of, Contains none of, Is empty, Is not empty. Lookup = Equals, Not equal to, Is empty, Is not empty. Owner offers 'Current user'. The Filter panel offers the same operators (e.g. Lead Status). Notes: Approval Status (system pick list) has no Is empty / Is not empty; the Deals Closing Date field was not found by label in the editor.</t>
+  </si>
+  <si>
+    <t>Run as ALT1, 7 values x 6 operators saved on 'QA CV text-sweep'; in all 42 cases the grid (records?view_id) equals the module filter (records?filters=) and the stored value equals the typed value byte-for-byte. Rules: case-insensitive (D3 starts_with 'Q' -&gt; L01, L02, L04, L05; D7 equals 'QA CV ACME' -&gt; L01, L02); leading/trailing spaces trimmed at match time but stored as typed (D6 equals -&gt; L01, L02); D8 contains Arabic -&gt; L03; D10 ends_with emoji -&gt; L04; D12 SQL-like value treated as a literal (equals/contains 0, not_equal_to/does_not_contain all); D14 zero-width space kept, contains -&gt; L05 only. No 500.</t>
+  </si>
+  <si>
+    <t>Comment: L01 null, L02 empty string, L03 whitespace only, L04 'Call back'. is_empty -&gt; L01, L02, L05…L15 (null and empty string count as empty); is_not_empty -&gt; L03, L04 (whitespace-only counts as not empty); exact complement; L04 never in is_empty; both equal the module filter.</t>
+  </si>
+  <si>
+    <t>Deals D01 0, D02 9999.99, D03 10000, D04 10000.01, D05 empty, D06 -1, D07 15000, D08 1000000000. equals 10000 -&gt; D03; not_equal_to -&gt; D01, D02, D04, D05, D06, D07, D08 (empty included, same as module filter); greater_than -&gt; D04, D07, D08; less_than -&gt; D01, D02, D06; ≥ -&gt; D03, D04, D07, D08; ≤ -&gt; D01, D02, D03, D06; equals 9999.99 -&gt; D02; equals 10000.01 -&gt; D04. All equal the module filter.</t>
+  </si>
+  <si>
+    <t>View API accepts non-numeric Amount values ('abc', '15,000', '1e9') and stores them as raw strings that match nothing - Editor (Amount box is input type=number): Arabic-Indic digits and 'abc' leave the box empty and Save is blocked with 'Complete this row (field, operator and value) or remove it.'; '-1' saves and returns D06. FAIL (API): POST with value '15,000', Arabic-Indic '15000', '1e9' and 'abc' -&gt; all 201 Created, the raw string is stored and the view matches 0 records - 'abc' is not rejected (expected 400/422) and '15,000' / '1e9' are neither normalised (15000 / 1000000000) nor rejected.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-D05-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>is_empty -&gt; D05 only; is_not_empty -&gt; D01 (0), D02, D03, D04, D06, D07, D08 - never D05; equals 0 -&gt; D01 only. All equal the module filter.</t>
+  </si>
+  <si>
+    <t>FieldPermissions seeds RA1 29 Sep (D-6), RA2 30 Sep (D-5), RA3 3 Oct (D-2), RA4 5 Oct (D), RA5 6 Oct (D+1); D = 5 Oct 2026 Cairo. is D -&gt; RA4; is_before -&gt; RA1, RA2, RA3; is_after -&gt; RA5; is_between D-5..D -&gt; RA2, RA3, RA4 (bounds inclusive); is_not_between -&gt; RA1, RA5 (exact complement); is_between D..D -&gt; RA4. All equal the module filter.</t>
+  </si>
+  <si>
+    <t>Date-time 'today/yesterday/tomorrow' criteria use the UTC day instead of the tenant timezone (Cairo) - Date Time Permission seeds: T01 4 Oct 23:50, T02 5 Oct 00:10, T03 5 Oct 23:50, T04 6 Oct 00:10 Cairo (stored UTC). At 13:37 Cairo on 5 Oct: today -&gt; T03, T04 (expected T02, T03); yesterday -&gt; T01, T02 (expected T01); tomorrow -&gt; none (expected T04). The grid shows T04 as '06/10/2026 12:10 AM' inside the Today view. The relative operators use the UTC date, not the Cairo date. Grid and module filter agree. (The case's 23:50 / 00:10 run times were not needed: the UTC-vs-Cairo split shows at any time.)</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-D08-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>D = Mon 5 Oct 2026. Seeds W01 4 Oct, W02 5 Oct, W03 11 Oct, W04 12 Oct, W05 30 Sep, W06 1 Oct, W07 1 Nov, W08 31 Dec 2025, W09 1 Jan 2026, W10 1 Jan 2027. this_week -&gt; W02, W03; last_week -&gt; W01, W05, W06; next_week -&gt; W04; this_month -&gt; W01, W02, W03, W04, W06; last_month -&gt; W05; next_month -&gt; W07; this_year -&gt; all 2026 seeds; last_year -&gt; W08; next_year -&gt; W10. Week starts on Monday. All equal the module filter.</t>
+  </si>
+  <si>
+    <t>API (24 POSTs, Date Permission): last_n_days / next_n_days accept 1 and 3650, reject 0, 3651, -1, 1.5 (lower bound 1); age_in_days / due_in_days accept 0, 1, 3650, reject 3651, -1, 1.5 (lower bound 0). Rejected values -&gt; 422, no view created; accepted values give grid = module filter.</t>
+  </si>
+  <si>
+    <t>Seeds H01 now-30m, H02 now-2h, H03 now+30m, H04 now+2h. last_n_hours 1 -&gt; H01; 720 -&gt; H01, H02; next_n_hours 1 -&gt; H03; 720 -&gt; H03, H04; 721 -&gt; 422 'value must be a whole number of hours between 1 and 720'. Counts equal the module filter.</t>
+  </si>
+  <si>
+    <t>Seeds NA1 now-1h, NA2 now+1h, NA3 empty. before_now -&gt; NA1 only; after_now -&gt; NA2 only; NA3 in neither. Equal to the module filter.</t>
+  </si>
+  <si>
+    <t>Checkbox Permission: K01 true, K02 false, K03 never set. is_true -&gt; K01; is_false -&gt; K02, K03. Rule: a never-set checkbox counts as false; same as the module filter.</t>
+  </si>
+  <si>
+    <t>A pick list value removed from the field is not shown in the view editor (blank 'Value', no warning), although the view still filters on it - S1 = No Answer, S2 = Busy. equals S1 -&gt; L01, L15; not_equal_to S1 -&gt; the rest incl. empty-status L12; contains_any_of S1,S2 -&gt; L01, L02, L13, L14, L15; contains_none_of -&gt; the rest (all equal the module filter). OWNER added 'QA CV Temp' to Lead Status and set L12 to it; view equals 'QA CV Temp' -&gt; L12. OWNER removed the value again (back to 16 values). Reopened: the grid works and still returns L12 showing 'QA CV Temp', no crash. FAIL: the editor shows the row as 'Lead Status | Equals | Value' - the stored value is not shown (a normal value such as 'No Answer' is shown) and there is no notice that it is no longer an option. Also 2 console errors (403) when ALT1 opens the editor.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-D14-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Multi Select Permission has only two options ('1','2'), so A='1', B='2' and the case's {C} record could not be seeded. Seeds M01 {1}, M02 {1,2}, M03 {2}, M04 empty. contains_any_of 1,2 -&gt; M01, M02, M03; contains_all_of 1,2 -&gt; M02 only; contains_none_of 1,2 -&gt; M04 (empty counts as none of); is_empty -&gt; M04; is_not_empty -&gt; M01, M02, M03. Equal to the module filter.</t>
+  </si>
+  <si>
+    <t>Lookup criteria in the view editor take free text only (no record picker); a typed record name is saved literally and matches nothing - Seeds Q01 -&gt; contact X (QA CV C01), Q02 -&gt; X, Q03 -&gt; Y (QA CV C02), Q04 empty. API with the stored form '&lt;module id&gt;:&lt;record id&gt;': equals X -&gt; Q01, Q02; not_equal_to X -&gt; Q03, Q04 (empty included); is_empty -&gt; Q04; is_not_empty -&gt; Q01, Q02, Q03 - grid equals the module filter. FAIL (editor): the value for Lookup Permission is a plain text box ('Value for Lookup Permission') with no record search, picker or suggestions; typing the record name 'QA CV C01' saves the literal text and the view returns 0 records. A bare record id also matches nothing. A user cannot build a working lookup criterion in the editor.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-D16-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>ALT1 built 'QA CV owner-me' in the editor: Name starts with 'QA CV O0' + Owner Equals 'Current user' (picker option), shared with Everyone -&gt; POST value '$me', visibility everyone; stored value '$me'. OWNER (owns O01-O03) sees O01, O02, O03; test user 2 (owns O04-O06) sees O04, O05, O06; ALT1 sees none. Each equals that user's module filter on owner = own id.</t>
+  </si>
+  <si>
+    <t>As ALT1: tag 'QA CV VIP' created; L01 and L02 selected in the grid -&gt; Module actions -&gt; Manage Tags -&gt; 'QA CV VIP' -&gt; Apply tags -&gt; 'Tagged 2 records.'. View 'QA CV tags' (Full Name starts with 'QA CV' + Tags contains any of QA CV VIP): grid L01, L02 only; module filter the same.</t>
+  </si>
+  <si>
+    <t>View API accepts an operator that does not fit the field type (Amount 'contains' -&gt; 201) - Unknown field does_not_exist_c -&gt; 422 unknown_field 'That field does not exist on this module.'; unknown operator xor_like -&gt; 422 'not a supported operator'; PATCH with the unknown field -&gt; 422, control view unchanged; views list unchanged. FAIL: Deals 'QA CV wrong-type' with Amount (currency) + operator contains -&gt; 201 Created - an operator that is not valid for the field type is accepted.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-D19-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>3 rows (Full Name starts with 'QA CV L0'; Lead Status is not empty; Comment is empty), pattern untouched -&gt; stored pattern null; reopened editor shows 'Criteria Pattern ( 1 and 2 and 3 )'. Grid L01, L02, L05, L06, L07, L08, L09 = module filter with the three conditions ANDed.</t>
+  </si>
+  <si>
+    <t>An unbracketed criteria pattern is stored and redisplayed as typed instead of in its fully bracketed form - Rows: Lead Status = No Answer, Lead Status = Busy, Comment is not empty (+ Full Name starts with 'QA CV P' to isolate P01-P04). Pattern typed '1 or 2 and 3 and 4'. The help ('read from left to right') is present as a tooltip on the pattern help icon. Results P02, P03 - correct for ((1 or 2) and 3); P01 and P04 not returned. FAIL: the saved pattern is stored and reopened exactly as typed ('( 1 or 2 and 3 and 4 )'), not fully bracketed as ((1 or 2) and 3).</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-D21-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Upper-case 'AND' pattern is accepted by the editor and the API (case expects it to be rejected) - Editor: every invalid pattern disables the pattern Save and shows a specific message (e.g. 'Brackets are not balanced.'); the view Save is paused while the pattern is edited. API: every invalid pattern -&gt; 422 with a specific message (unbalanced, unexpected ')', two operators, ends unexpectedly, criteria 5 does not exist, criteria 3 missing, criteria 1 used twice, unknown word xor, nests deeper than 3 levels, at most 200 characters). FAIL: the upper-case pattern '1 AND 2 AND 3' is accepted by the editor and by the API (201), although the case lists it as invalid.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-D22-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Rows Lead Status = No Answer, Lead Status = Busy, Comment is not empty, Full Name starts with 'QA CV P'; pattern '((1 or 2) and 3) and 4'. Stored and re-saved pattern identical; results P02, P03 before and after re-save = union of (No Answer AND comment) and (Busy AND comment) from the module filter.</t>
+  </si>
+  <si>
+    <t>Arabic UI: the criteria pattern '(1 or 2) and (3 or 4)' is displayed as '( and (3 or 4) (or 2 1) )' - Run as ALT1. 'QA CV rtl-pattern' with rows Lead Status = No Answer, Lead Status = Busy, Comment is not empty, Full Name starts with 'QA CV' and pattern '(1 or 2) and (3 or 4)'. UI switched to Arabic (dir=rtl). FAIL: the editor shows the pattern as '( and (3 or 4) (or 2 1) )' - brackets and token order scrambled (English text inside an RTL line without isolation). Results identical in Arabic and English (9 records). Switched back to English afterwards.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-D24-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Last Activity' in view criteria is the record's modified time; adding a note does not update it - 'Last Activity' is offered in the criteria field list with the date-time operators. FAIL: it is the record's modified time, not an activity time - a note added to QA CV L02 (POST notes 201) left last_modified_at unchanged (08:47:45Z) and a 'last 1 hour' Last Activity filter does not return L02.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-D25-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Run as ALT1. Seeds: C01 &lt;- D01 (Stage negotiation, via Connected To), C02 &lt;- D02 (qualification), C03 no deals. 'QA CV with-negotiation' (First name starts with 'QA CV' + with Deals, any link field, Stage equals negotiation) -&gt; C01 only. Stored related_criteria: [{module_id: Deals, link_field: null, mode: 'with', criteria: stage equals negotiation}]. The same block built in the editor ('QA CV link-field') produced the identical related_criteria body. (The records filter API has no related-criteria parameter, so the cross-check is the expected set.)</t>
+  </si>
+  <si>
+    <t>QA CV without-deals' (First name starts with 'QA CV' + without Deals, any link field) -&gt; C03 only; C01, C02 (and C04, linked to D08) not returned.</t>
+  </si>
+  <si>
+    <t>Precondition not met: the case needs a user who can see contact C04 but not deal D08. C04 was given to test user 1 (User profile), but test user 1 can also open D08 (GET 200), so the deal is not hidden. Recorded anyway: as test user 1, without Deals -&gt; C03 only; with Deals -&gt; C01, C02, C04; no D08 data in either response.</t>
+  </si>
+  <si>
+    <t>Contacts' link fields from Deals: Contact, Connected To, Lookup ('Lookup 2' does not exist on Deals; 'Lookup' used). Seeds: C01 &lt;- D01 via Connected To, C02 &lt;- D03 via Lookup, both Stage negotiation (Stage is labelled 'Test-Stage'). 'QA CV link-field' built in the editor (with Deals, Linked through Any link field, Test-Stage equals negotiation) -&gt; saved 201. Any link field -&gt; C01, C02; Connected To -&gt; C01 only; Lookup -&gt; C02 only.</t>
+  </si>
+  <si>
+    <t>Editor (Contacts): related blocks Deals, Tasks, Calls added; 'Add condition' then disabled. API: 3 related modules -&gt; 201; a 4th related_criteria entry -&gt; 422 'A view may use at most 3 related modules.'; no view created. Note: the disabled 'Add condition' shows no tooltip/message in the editor.</t>
+  </si>
+  <si>
+    <t>Editor: Deals block with 'Specify Deals criteria' - 3 rows, then 'Add criteria row' in the block is disabled. API: 3 rows (Stage = negotiation, Amount &gt; 0, Deal name starts with 'QA CV') -&gt; 201; 4 rows -&gt; 422 'At most 3 criteria rows are allowed.'; no view created.</t>
+  </si>
+  <si>
+    <t>Module with no related modules: the editor still shows an empty related block and an enabled 'Add condition' - Tasks and Subscriptions both have related modules, so module 'test' (no related modules) was used. New custom view -&gt; Related modules criteria shows 'No module has a lookup to test yet.' (module name filled in). FAIL: an empty related block is still rendered and 'Add condition' stays enabled and adds more empty blocks (1 -&gt; 2). Expected: no related block can be added.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-E07-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Editor (Contacts): six rows 'Account › Created At · Is not empty' -&gt; Save refused with 'At most 5 criteria rows can use fields of lookup modules.' (no POST). API: 5 lookup-path rows (account_id.accounts.created_at) -&gt; 201; 6 -&gt; 422 too_many_lookup_fields 'At most 5 criteria rows may use fields of lookup modules.'</t>
+  </si>
+  <si>
+    <t>Deleted criteria field: no banner on the view's list page (only in the editor, by API name) while the view keeps filtering on the deleted field - OWNER created number field 'QA CV Temp Number' (qa_cv_temp_number); L01 = 5, L02 = 0. ALT1 view 'QA CV temp-field' (First name starts with 'QA CV' + QA CV Temp Number &gt; 1) -&gt; L01. OWNER deleted the field (204). The view still runs with no error and still returns only L01 (the stored criterion on the deleted field keeps filtering; Name-only filter gives 19 QA CV rows). FAIL: the list page shows no banner at all; only the editor shows 'Some fields in this view's criteria are deleted or hidden from you: qa_cv_temp_number.' - with the API name, not 'QA CV Temp Number' - and the row reads 'Select a field'. 2 console errors (403) on the page.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-E09-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Precondition not met: Percent Permission is not hidden for the User profile (test user 1 receives the field definition), and the Profiles settings page is not reachable on staging-crm.taviportal.com ('You don't have access to CRM'), so the field could not be hidden for this case.</t>
+  </si>
+  <si>
+    <t>Precondition not met: Percent Permission is not hidden for the User profile, and the Profiles settings page is not reachable on staging-crm.taviportal.com ('You don't have access to CRM').</t>
+  </si>
+  <si>
+    <t>A user without the review permission can filter by review_status through the views API (condition accepted and applied), exposing review data - Field list: ALT1 (CRM Admin) is offered 'Review Status'; test user 1 (User profile, no review permission) is not (only 'Approval Status'). FAIL: as test user 1, POST view 'QA CV review-gate' with review_status equals 'approved' -&gt; 201, stored as sent, and the view filters on it: 4 of test user 1's 20 visible leads are returned (pending / rejected / not_submitted -&gt; 0). The records filter API also accepts review_status from test user 1. A user without the review permission gets review data through a view.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-E12-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Manage Columns on a view with chosen columns offers no hidden/available fields, so a column (e.g. Comment) cannot be added - Run as ALT1 on 'QA CV columns-f' (columns Full Name, Lead Status, Company). Manage Columns lists only VISIBLE (4): Full Name, Lead Status, Company, Lead Owner - no hidden/available list. Hiding Lead Status works (column disappears, banner 'You changed the columns for this view. Only you see this change.'). Full Name's Hide button is disabled (locked). There is no reset option inside Manage Columns; the banner's 'Use the view's columns' restores Full Name, Lead Status, Company. FAIL: Comment cannot be shown - Manage Columns offers no way to add a field that the view does not already show.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-F01-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>ALT1 owns 'QA CV shared-cols' (Full Name, Lead Status, Company, Comment), shared with Everyone. Test user 2 hides Company -&gt; 'You changed the columns for this view. Only you see this change.'; test user 2's list-preferences hold the override (hiddenKeys company); no 'Save to view' for that user. ALT1 still sees Full Name, Lead Status, Company, Comment; the view's row_version is unchanged (1). Test user 2 then chose 'Use the view's columns'.</t>
+  </si>
+  <si>
+    <t>Manage Columns cannot add a column to a view (so a new column cannot be saved to the view) - Run as ALT1 on 'QA CV save-cols' (Full Name, Lead Status, Company). Step 1 (add Comment) cannot be done: Manage Columns does not offer Comment (same cause as F01). Tested the rest with a hide instead: hide Company -&gt; banner with 'Save to view' and 'Use the view's columns'; Save to view -&gt; settings.columns first_name, lead_status, owner and row_version 1 -&gt; 2; then hide Lead Status -&gt; 'Use the view's columns' restores the view's columns and the override is gone from list-preferences. Note: 'Save to view' also wrote the default Lead Owner column into the view.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-F03-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>List preferences accept more than 50 column overrides (51 stored); no oldest-dropped or 4xx rule - As ALT1: 51 Leads list views (incl. 'QA CV ov-NN'); PUT list-preferences with a column override for each of the 51 -&gt; 200; GET shows all 51 stored (first and last both kept) - neither the oldest dropped nor the 51st rejected; the 50-override limit is not enforced. ALT1's preferences restored afterwards (PUT 200).</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-F04-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Header sort as ALT1. Company asc: QA CV Acme, qa cv acme, QA CV Rocket, QA​CV Zero, Arabic, then empties; desc: Arabic … QA CV Acme, qa cv acme, then empties. Amount asc: -1, 0, 9,999.99, 10,000, 10,000.01, 15,000, 1,000,000,000, then empty (D05); desc the exact reverse with empty last (numeric order). Date Permission asc 29/09, 30/09, 03/10, 05/10, 06/10; desc reversed. Empty values always last. Observation: opening a FieldPermissions view by link while the page is on the Standard layout shows another view; it had to be picked in the picker after switching layout.</t>
+  </si>
+  <si>
+    <t>Toolbar sort label shows API names ('Sort: amount desc') instead of the field label and direction - 'QA CV sort-deals': header Amount descending and toolbar Sort (Amount, Descending, Apply) give the identical order D08, D07, D04, D03, D02, D01, D06, D05 (empty last). FAIL: the toolbar label reads 'Sort: amount desc' - internal field and direction keys, not 'Amount' / 'Descending' as in the sort dialog.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-F06-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Rows per page offers 10/25/50/100 only - 200 is missing - All Leads (109 records): 10 -&gt; 10 rows, 11 pages; 25 -&gt; 25 rows, 5 pages; 50 -&gt; 50 rows, 3 pages; 100 -&gt; 100 rows, 2 pages; pageSize in list-preferences follows the last choice (set back to 25). FAIL: 200 is not offered in 'Rows per page' (options 10/25/50/100) although the case and spec list it.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-F07-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>QA CV count' (Full Name starts with 'QA CV L'; this run's seed set is L01-L15): header '15 records', pages 10 + 5 rows (15 unique), records filter API total 15.</t>
+  </si>
+  <si>
+    <t>All Leads, 25 per page: the header checkbox ticks every selectable row on page 1 (22 - the other 3 are locked records without a checkbox), bar '22 selected'; page 2 has no row ticked (bar keeps the page-1 count); back on page 1 unticking clears all rows and the bar.</t>
+  </si>
+  <si>
+    <t>Row selection is kept when switching to another view (bar still '3 selected') - 'QA CV select': L01, L02, L03 selected, bar '3 selected'. Switched to All Leads (URL ?view=All Leads, picker shows All Leads): L01, L02, L03 are still ticked and the bar still shows '3 selected'; switching back to 'QA CV select' - still 3 selected. FAIL: the selection is not cleared when the view changes (the earlier run on crm.taviportal.com cleared it).</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-F10-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>QA CV mass': selected QA CV L03 and L04 (L01/L02 used other selectors in this build; same check). Module actions -&gt; Mass Update ('Apply the same values to 2 selected records') -&gt; Comment = 'QA CV mass-updated' -&gt; Update records -&gt; '2 records updated'. API: only L03 and L04 changed; L01, L02, L05-L15 unchanged.</t>
+  </si>
+  <si>
+    <t>QA CV export' (Full Name starts with 'QA CV L'; columns Full Name, Lead Status, Company). Export dialog: 'All records (15)' / 'Current page only'; 'Visible columns (4) - the columns shown in the table, in the same order, plus Tags' / 'All fields'. Exported with defaults -&gt; leads-export-2026-10-05.xlsx: 15 data rows = exactly the view's records (QA CV L01-L15); columns Full Name, Lead Status, Company, Lead Owner, Tags. Recorded rule: export follows the view's criteria and visible columns.</t>
+  </si>
+  <si>
+    <t>As ALT1: Company is read-only for this profile (no inline Edit field; locked on the form), so Full Name was used. Inline edit 'QA CV L03 Inline' -&gt; saved, API shows it. 256 characters -&gt; saved (no length limit on Full Name; the same record API the form uses) - name restored afterwards. FieldPermissions record QA CV K01: clearing the required Single Line Permission inline -&gt; refused with 'This field is required', popover stays open, stored value 'qa' unchanged. No partial save.</t>
+  </si>
+  <si>
+    <t>QA CV empty' (Full Name equals 'QA CV no-such-record'): '0 records' with the empty state 'No Leads yet - Create your first Lead to get started'; no alert or toast; records filter API total 0. Note: the empty-state text speaks of no leads at all rather than 'no records match this view'.</t>
+  </si>
+  <si>
+    <t>Run as ALT1 (CRM Admin; the Owner session is in use by another operator). 'QA CV clone-src' (everyone; Lead Status equals Interested AND Company contains 'QA'; 6 columns; sort first_name asc; page size 50). Tab menu: Edit, Pin view, Clone, Close view, Delete view. Clone -&gt; editor with 'Copy of QA CV clone-src' -&gt; renamed 'QA CV clone-src copy' -&gt; 'Custom view "QA CV clone-src copy" saved.'. Copy: owner ALT1, visibility private, Created by me; criteria, columns, sort, page size identical. Source unchanged (name, everyone, settings, row_version 1). Note: the explicit pattern '1 and 2' came back as null on the UI copy (the editor drops a pattern equal to the default AND; same results). A source with '1 or 2' keeps its pattern on clone (2 = 2 records).</t>
+  </si>
+  <si>
+    <t>ALT1 shares 'QA CV shared-src' with Selected users = test user 1 (Shared with me for that user). Test user 1: tab menu -&gt; Clone -&gt; editor -&gt; 'QA CV shared-src copy' saved. Copy: owner_user_id = test user 1, private, created_by_me; not visible to ALT1; source unchanged (settings and row_version). Criteria and sort equal; columns equal except Company, which test user 1 has no read access to (Company is absent from every record that user can read) - the API clone drops it too, so this follows field security. Observation: test user 1 (User profile WITH Manage Shared Views) gets can_edit/can_delete = true on a view shared with them and could rename it via PATCH (200; reverted). CVR-SHARE-5 says only owner and administrators may edit; A04 (recipient without Manage Shared Views) passed. Needs a product decision whether Manage Shared Views grants edit on others' shared views.</t>
+  </si>
+  <si>
+    <t>All Leads (is_system true). Tab menu: Edit columns, Pin view, Clone (disabled, title 'You cannot clone a system-defined view.'), Close view. POST …/views/{All Leads}/clone -&gt; 409 SYSTEM_VIEW_LOCKED 'This is a system-defined view. Only its columns, sort and page size can be changed.'; view count unchanged.</t>
+  </si>
+  <si>
+    <t>Clone in the picker row menu (dropdown layout) does nothing - API: POST …/clone twice -&gt; 201 'Copy of QA CV clone-src' and 201 'Copy of QA CV clone-src (2)'. Tabs layout: Clone from the tab menu twice -&gt; editor suggests 'Copy of QA CV clone-src (3)' / '(4)', saved with toasts. No 500, no VIEW_NAME_TAKEN, no duplicate names among ALT1's views. FAIL (reproduced from the 4 Oct run): in the dropdown layout, the view's 'Actions for QA CV clone-src' menu inside the picker offers Clone, but clicking it does nothing - no POST, no editor, no toast.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-G04-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>ALT1 pinned 'QA CV pin-a', 'QA CV pin-b' and All Leads from the tab menu: picker starts with PINNED VIEWS: QA CV pin-a, QA CV pin-b, All Leads* (pin_order 140/150/160) and all three show as tabs. Test user 1's picker shows no Pinned views group (ALT1's pins are per user). Test user 1 pinned the shared 'QA CV shared-src' -&gt; pinned for that user only; ALT1's view of it is not pinned and ALT1's picker is unchanged. Unpin view on every pinned view -&gt; views leave the group; with nothing pinned the Pinned views group is gone.</t>
+  </si>
+  <si>
+    <t>The 15-pinned-views limit is not enforced (16th pin accepted in UI and API) - ALT1 had 0 pins; pinned QA CV pin-01…pin-15 (15 pinned). Tab menu on 'QA CV pin-16': Pin view enabled; clicking it pins the view with no message (16 pinned). PUT …/views/{pin-16}/pin -&gt; 204. GET: 16 pinned, pin-16 pinned=true; Pinned views group lists 16. Expected a refusal stating the 15 limit and a 4xx. All pins removed afterwards.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-G06-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>All Leads 114 records. 'QA CV delete-me' -&gt; Delete view: 'Delete custom view? Are you sure you want to delete the "QA CV delete-me" custom view? It moves to the Recycle Bin; its records are not affected.' Cancel -&gt; view kept (GET 200). Delete -&gt; '"QA CV delete-me" was deleted.', GET 404, gone from tabs and picker; Recycle Bin lists it (Custom View, record_label 'QA CV delete-me'); All Leads still 114.</t>
+  </si>
+  <si>
+    <t>QA CV restore-me' (everyone, criteria, 3 columns, sort first_name asc, page size 25) row_version 1, not pinned. Deleted (204) -&gt; Recycle Bin item 'QA CV restore-me' (Custom View, expires 4 Dec 2026). Settings &gt; Data &gt; Recycle Bin -&gt; Restore -&gt; 'Restore items? Restore 1 item?' -&gt; Restore. GET: same id, same name, visibility everyone, identical settings, pinned false; row_version 1 -&gt; 3 (delete and restore each bump it).</t>
+  </si>
+  <si>
+    <t>All Leads: is_system true, can_delete false, row_version 3. DELETE -&gt; 409 SYSTEM_VIEW_LOCKED ('This is a system-defined view. Only its columns, sort and page size can be changed.'). GET afterwards 200, unchanged (row_version 3); not in the Recycle Bin.</t>
+  </si>
+  <si>
+    <t>QA CV last-used' selected (lastListViewId = its id). Opened Deals; DELETE the view (204). Opened Leads: All Leads selected, no error page or toast, 'QA CV last-used' not in tabs. Network: 403 /telephony/status (unrelated) and two 400s on GET /modules/{Leads}/views while the page loaded (not visible to the user).</t>
+  </si>
+  <si>
+    <t>Test user 1 owns 'QA CV user-public' (everyone) and has it selected. Deleted by ALT1 (CRM Admin - deviation: Owner session in use by another operator): GET can_delete true, listed under Public views; tab menu Delete view -&gt; confirmed. Test user 1's GET 404; after reload test user 1 is on All Leads and the picker no longer lists the view.</t>
+  </si>
+  <si>
+    <t>ALT1's 'QA CV selected-share' shared with test user 1 and test user 2; test user 1 had it open (GET 200). ALT1 edited it, removed test user 1 ('Remove test user 1'), kept test user 2, saved ('Custom view "QA CV selected-share" saved.'; shared_user_ids = test user 2 only). Test user 1 reloading the view link lands on All Leads; GET view -&gt; 404 NOT_FOUND 'Not Found'; records with view_id -&gt; 404 (no records exposed). Note: the API message is the generic 'Not Found', not 'View not found - This view was deleted, or it is not shared with you.', and the UI falls back silently.</t>
+  </si>
+  <si>
+    <t>Contacts has 0 Kanban views (API). Clicking 'Kanban view' opens the 'New Kanban view' settings form directly (Name, Categorize by, Aggregate by, Header style, Select fields, Share with); Cancel returns to the list. The 'No Kanban views yet' empty state is never shown - Zoho does the same (opens 'Kanban View - Settings' directly), so the result matches the reference product (same as the 4 Oct run).</t>
+  </si>
+  <si>
+    <t>QA CV leads-by-status' created in the UI (Categorize by defaults to Lead Status). Columns: the 16 Lead Status values in exactly the field order (No Answer … Cold Customer), then Unaccounted last. Unaccounted shows 55 = the number of leads with an empty Lead Status (API). No QA CV L seed has an empty Lead Status on staging, so step 5 was checked through the count. Observation: a 17th column 'QA CV Temp' sits before Unaccounted for QA CV L12, which still holds a value removed from the pick list (see I04).</t>
+  </si>
+  <si>
+    <t>New Kanban view &gt; Categorize by offers: Lead Status (status), Reason, Lead Source, Complaint Reason (pick lists). Hint 'Single-value pick list, status or radio-button fields only.' No multi-select, text, number, date, user or lookup field is offered.</t>
+  </si>
+  <si>
+    <t>Every module on NDC-Staging has a groupable field - at least the system 'Approval Status' pick list (Leads, Contacts, Deals, Accounts, Tasks, Calls, Meetings, Subscriptions, test). The 4 Oct run showed that a new custom module with text fields only still gets Approval Status, so a module with no pick list/status/radio field cannot exist and the two messages cannot be reached.</t>
+  </si>
+  <si>
+    <t>Kanban view form: an over-long name gets only 'The view is not valid.' - the 120-character limit is not shown or enforced in the field - Empty name -&gt; 'A view name is required.' (no request; spec wording 'Give the view a name.'). 120-character name saves. 121 characters: the field has no maxlength, Save sends POST -&gt; 422 INVALID_VIEW name too_long 'A view name may be at most 120 characters.', but the form only shows the generic 'The view is not valid.' - the user is not told the name is too long or what the limit is. API POST kind kanban with 122 characters -&gt; 422 (no 500). Name 'QA CV &lt;img src=x onerror=alert(1)&gt;' saved; shown as literal text in the chooser and in Manage Kanban views; no &lt;img&gt; element rendered, no alert.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-H05-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Default card fields: Full Name, Phone, Email (3). The Standard layout offers 6 more (Company, Lead Owner, Reason, Comment, Lead Source, Complaint Reason) - 9 in total, so an 11th cannot be reached in the UI; API PATCH with 11 card_fields -&gt; 422 settings.card_fields too_many 'A card can show at most 10 fields.' (stored stays 10). Move up twice moved Complaint Reason above Comment and Lead Source; saved order respected (card: title, Full Name, phone, company, owner …). Hint 'The record name always shows first.' - the record name is the card title and cannot be removed (the Full Name card field itself can be moved/removed).</t>
+  </si>
+  <si>
+    <t>QA CV kb-status' &gt; Edit &gt; Header style Mono color &gt; Save &gt; reload: all 18 column headers use the same blue accent (settings.header_style mono). Multi color &gt; Save &gt; reload: headers use 12 distinct colours (multi stored).</t>
+  </si>
+  <si>
+    <t>ALT1 (CRM Admin) sees Share with: Only me, Everyone, Selected users. 'QA CV kb-share' shared with test user 2 (profile 'test', no Manage Shared Views) - it appears in test user 2's Kanban chooser. Test user 2's new Kanban form offers only 'Only me' (checked) with 'You need the Manage Shared Views permission to share a view with other people.' Test user 2's API POST kind kanban visibility everyone -&gt; 403 PERMISSION_DENIED. (Wording differs from the spec text 'You can create views for yourself…' but the rule holds.)</t>
+  </si>
+  <si>
+    <t>Kanban chooser does not label other users' views with 'Shared by &lt;name&gt;' - 'QA CV kb-status' (Lead Status) and 'QA CV kb-second' (Lead Source) both exist; switching in the chooser rebuilds the board: 16 status columns + QA CV Temp + Unaccounted vs chat, web, referral, other + Unaccounted. Test user 1's 'QA CV kb-user1' (shared with everyone) is listed in ALT1's chooser as just 'QA CV kb-user1' - no 'Shared by &lt;name&gt;' label, and own and shared views are not distinguished.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-H10-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>QA CV kb-edit' by Lead Status (16 + QA CV Temp + Unaccounted). Edit &gt; Categorize by Lead Source &gt; Save: board rebuilt with chat, web, referral, other + Unaccounted (= the 4 Lead Source values); GET settings.categorize_field = lead_source.</t>
+  </si>
+  <si>
+    <t>All Leads 118. 'QA CV kb-delete' &gt; Edit this Kanban view &gt; Delete this view: inline confirmation 'Delete view? "QA CV kb-delete" moves to the Recycle Bin. Its records are not affected.' Cancel -&gt; view kept (GET 200). Delete -&gt; 'View deleted', GET 404, gone from the chooser, in the Recycle Bin as 'QA CV kb-delete (Kanban View)'; All Leads still 118.</t>
+  </si>
+  <si>
+    <t>Chooser &gt; Manage Kanban views opens 'Manage Kanban Views' (View Name, Used Field, Layout, Shared To, Last Modified By, Created By, Actions) listing 10 views - exactly the names GET ?kind=kanban returns (incl. QA CV kb-status). 'Create Kanban View' opens the 'New Kanban view' form; closed without saving.</t>
+  </si>
+  <si>
+    <t>Records whose value is beyond the 75-column cap vanish from the Kanban board; board-summary says truncated=false - Field 'QA CV Picklist80' (v01…v80) created on Leads; QA CV L01 = v76, QA CV L02 = v80. Kanban 'QA CV kb-80': notice 'Only the first 75 values are shown as columns.'; 75 value columns v01–v75 + Unaccounted (76). FAIL (reproduced from 4 Oct): L01 and L02 appear nowhere on the board - no v76/v80 column, not in Unaccounted, no 'Other values' column (PRD P1-7). board-summary returns columns v76 count 1 and v80 count 1 but truncated=false.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-H14-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Leads 'QA CV kb-status': Aggregate by offers only 'None' (no number/currency field on the Leads Standard layout), so totals were checked on the Deals board. Leads first-load header counts (No Answer 8, Busy 21, Switched Off 6, Wrong Number 7, Interested 13, Follow Up 3, WhatsApp 1, Cold Customer 1, QA CV Temp 1, Unaccounted 60) equal the board-summary the page requested, Unaccounted = unaccounted; Interested 13 = list filtered to Interested (13). Deals 'QA CV deals-by-stage' (Stage, Amount): qualification 35 / 5,516,962,114,653.99, negotiation 9 / 16,893,538,880.00, proposal 3 / 1,000,025,000.01, closed_won 2 / 85,000.00 - identical to board-summary counts and sums. Note: the page calls board-summary with the list view id (All Leads) as view_id; calling it with the Kanban view's own id returns 404.</t>
+  </si>
+  <si>
+    <t>No Lead Status column holds more than 100 records (largest: Unaccounted 60, Busy 21); on Deals the largest column is qualification with 35. Load more / 100-card paging cannot be exercised on NDC-Staging without bulk-creating records.</t>
+  </si>
+  <si>
+    <t>No seed had an empty Lead Status, so QA CV L15's Lead Status was cleared for the test (restored to No Answer afterwards). On 'QA CV kb-status' QA CV L15 is in the Unaccounted column; Unaccounted header 60 = board-summary unaccounted 60.</t>
+  </si>
+  <si>
+    <t>A record holding a removed pick-list value is shown in an unmarked extra column - no 'no longer an option' flag - QA CV L12 holds 'QA CV Temp', a value added to Lead Status and then removed earlier in this run. Board 'QA CV kb-status': L12 is still shown, in an extra column 'QA CV Temp' (count 1) placed before Unaccounted. FAIL (reproduced from 4 Oct): no 'This value is no longer an option of the field' marker anywhere - not in text, title, aria-label or a tooltip on the column header or the card; the stale column looks like any normal value column and offers 'Create Lead'.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-I04-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Deals Kanban by Stage has no pipeline picker, ignores the pipeline's stages and shows no stage probability - Deals Standard layout has one pipeline 'Standard' (qualification, needs_analysis, proposal, negotiation, closed_won, closed_lost); the Test layout has two ('Standard Pipeline', 'Test-Pipeline copy'). Board 'QA CV deals-by-stage' (Standard) and 'QA CV deals-test-layout' (Test): no pipeline picker on either board (only the Layout picker); both show all 11 Stage pick-list values (test-01, test-02, qualification … closed_lost_to_competition) instead of the chosen pipeline's stages; no stage header shows 'Probability N%' (the pipeline API carries no probability). Column titles show raw stage keys (needs_analysis, closed_won).</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-I05-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>QA CV L03 set to Interested for the test (original Switched Off, restored). Board: Interested 14, Follow Up 3. Mouse drag L03 Interested -&gt; Follow Up: one PATCH on the record, toast 'Record updated successfully'; headers Interested 13, Follow Up 4, card in Follow Up; board-summary Interested 13 / Follow Up 4; API lead_status Follow Up. Audit events list the change (actor Mahmoud Mohamed, lead_status Interested -&gt; Follow Up). No active email workflow on Leads/Deals.</t>
+  </si>
+  <si>
+    <t>Precondition not met: Lead Status is not required on the Leads layout (required=false). Observation: dragging QA CV L04 (Interested) to Unaccounted sends a PATCH and clears Lead Status ('Record updated successfully', API empty), but right after the drop the card was still drawn under Interested. L04 restored to Wrong Number.</t>
+  </si>
+  <si>
+    <t>board-summary group_by_blueprint_governed = true for Deals Stage, but the only active blueprint ('AEX-01', another operator's) has entry criteria Amount &gt;= 15,000 AND Deal Name contains 'AEX-01' - no QA CV deal is under it. Moving QA CV D02 qualification -&gt; negotiation on the board saved directly (PATCH 200, no transition dialog), which is expected for a record outside the blueprint. Testing a record under the blueprint would mean entering the other operator's blueprint; D02 restored to qualification.</t>
+  </si>
+  <si>
+    <t>Dropping a deal on Closed Won/Lost opens no closing dialog - the move just fails with 'Closing Date is required' - QA CV D03 (negotiation) moved to closed_lost on the board: no closing dialog opens; a PATCH is sent and refused - toast 'Closing Date is required to close a deal.'; the card returns to negotiation and Stage is unchanged. Same for closed_won. The user is never offered a dialog to fill the mandatory closing fields, so a deal cannot be closed from the board at all.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-I09-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Network throttled through the DevTools protocol (2 s latency, 50 KB/s), board reloaded: cards first appeared after 51 s, with no loading indicator left; a keyboard move of QA CV L05 to Follow Up at that moment was accepted (PATCH, 'Dropped … into Follow Up.'). Cards only become draggable once the board has loaded, so a drag 'before loading finishes' and the refusal message could not be produced (same as 4 Oct). L05 restored to Interested.</t>
+  </si>
+  <si>
+    <t>Kanban move from a stale board overwrites a newer change with no conflict check - Two tabs (same user, separate pages) on 'QA CV kb-status'. Tab A: QA CV L06 Interested -&gt; Follow Up (saved). Tab B, not refreshed (still showing L06 in Interested): moved L06 to WhatsApp Follow Up -&gt; PATCH accepted, 'Record updated successfully'. Final Lead Status WhatsApp Follow Up; audit shows Interested-&gt;Follow Up then Follow Up-&gt;WhatsApp Follow Up. No conflict, no 'Could not move the record' and no board refresh in tab B - the stale move silently overwrote A's change (the PATCH carries no version check). L06 restored to Interested.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-I11-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>QA CV L07 dragged ~60 px and dropped back inside Interested: no PATCH/PUT/POST on records, Interested count 13 -&gt; 13, Lead Status still Interested.</t>
+  </si>
+  <si>
+    <t>QA CV L08 card focused; Enter picks it up, ArrowRight -&gt; live region '… is over Follow Up.', Enter drops -&gt; 'Dropped … into Follow Up.', 'Record updated successfully', PATCH 200; Interested 13 -&gt; 12, Follow Up 3 -&gt; 4; API Follow Up (same save path as a drag). The Unaccounted half does not apply (Lead Status not required). Accessibility note (L05): announcements read the record UUID, not its name. L08 restored.</t>
+  </si>
+  <si>
+    <t>Interested collapsed and expanded; 'Collapse all columns' collapses all 18, 'Expand all columns' expands all 18. Follow Up collapsed; QA CV L09 dragged onto the collapsed Follow Up column -&gt; PATCH; after expanding, counts Interested 13 -&gt; 12, Follow Up 3 -&gt; 4 and the API holds Follow Up. L09 restored to Interested.</t>
+  </si>
+  <si>
+    <t>Deals board 'QA CV deals-by-stage': the negotiation column's 'Create Deal' link opens /records/new?layout=&lt;Standard&gt;&amp;prefill_field=stage&amp;prefill_value=negotiation; form shows Layout Standard, Pipeline Standard, Stage negotiation (Probability prefilled 70). Saved 'QA CV D09' -&gt; 201; API stage negotiation, pipeline = Standard (5170500c…).</t>
+  </si>
+  <si>
+    <t>Interested has 13 cards loaded; 'Select all loaded records in Interested' -&gt; bulk bar '13 selected'; 0 cards selected in other columns; unticking clears the bar. Accessibility issue (L05): every card checkbox carries the column select-all name 'Select all loaded records in &lt;column&gt;'.</t>
+  </si>
+  <si>
+    <t>QA CV deals-by-stage' shared with Everyone (reverted to private afterwards). Test user 1's board, Deals list (49) and board-summary all agree (qualification 35, negotiation 9, proposal 3, closed_won 2, same sums) - but they are identical to ALT1's: test user 1 can open every deal, so the precondition 'some QA CV deals are not accessible to USER' is not met and the restriction cannot be shown.</t>
+  </si>
+  <si>
+    <t>Board open with Interested 13 / Follow Up 3. QA CV L10 changed to Follow Up from outside the board (API PATCH 200). Without reload the headers updated after 23 s: Interested 12, Follow Up 4. L10 restored.</t>
+  </si>
+  <si>
+    <t>Leads had 0 split views (API). 'Split view' opens the 'Create Split View' form directly (Name, View based on Picklist/User or Criteria, Split by, Splits 'The selection is limited to a maximum of 10 values.', Select columns, Share with); Cancel closes it. No 'No split views yet' empty state - Zoho does the same (goes straight to the create form), so this matches the reference and the case's expected text looks outdated.</t>
+  </si>
+  <si>
+    <t>QA CV split-status' created in the UI split by Lead Status (Busy, Interested, Follow Up): sections Busy 21, Interested 13 (14 after J04), Follow Up 3 = API counts. Collapse/Expand per section works. Edited to split by Owner (3 users): sections 0, 8, 10 = API owner counts. Criteria mode: 'New Split' with its own name, criteria rows and per-split columns ('Apply for all splits'); saving with one split is refused 'A split view needs at least 2 splits.' (criteria splits were not completed - the field picker is a custom control). Columns: in Picklist/User mode a section's 'Section options &gt; Manage columns' opens the whole Edit Split View form and the columns are 'common for all splits' (the same rule and wording as Zoho); per-section columns exist only for criteria splits. Observation: the form saves a split view with zero columns, after which sections show only #, Tags and Source (no record names).</t>
+  </si>
+  <si>
+    <t>Split view criteria: the 'Add criteria row' button silently disables at 10 rows - no limit message - Values: the 'Select Splits' chooser disables the 11th value once 10 are ticked, with 'The selection is limited to a maximum of 10 values.'; API PATCH with 11 splits -&gt; 422 settings.splits too_many 'A split view may have at most 10 splits.' Criteria: 'Add criteria row' becomes disabled after 10 rows. FAIL: no message is shown for the criteria limit - no text, tooltip, title or aria-describedby (the 4 Oct build had the title 'A maximum of 10 criteria rows is allowed'). Maximums recorded: 10 values, 10 criteria rows.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-J03-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Records per split = 10 (options 10/25/50): Busy (21) shows 10 rows, '1–10 of 21', 3 pages. 'Create Lead' in the Interested section opens /records/new?…&amp;prefill_field=lead_status&amp;prefill_value=Interested; saved 'QA CV L16' (name QA CV L13 already exists on staging) -&gt; 201, API lead_status Interested; Interested section count 13 -&gt; 14.</t>
+  </si>
+  <si>
+    <t>Created 'QA CV &lt;img src=x onerror=alert(1)&gt;' as a Leads list view (criterion Full Name contains the payload), a Leads split view and a Deals Kanban view (all 201). Shown as literal text in the Leads picker and selected-view button, Manage custom views, the split chooser, the Deals Kanban chooser and Manage Kanban views (and, from H05, in the Leads Kanban chooser/manage dialog). No &lt;img src=x&gt; element anywhere, no alert/dialog fired, no request to /x. The Audit Log page (/settings/security/audit-log) did not list the view name. Not reached: the delete dialog - in the dropdown layout the picker row menu's 'Delete view' does nothing (no dialog, view kept; same defect family as G04), and the Work Queue step was not run.</t>
+  </si>
+  <si>
+    <t>ALT1's private 'QA CV owner-private'. As test user 1: GET, PATCH {name:'QA CV hacked'}, DELETE, POST …/clone, PUT …/pin, DELETE …/pin and records?view_id all -&gt; 404 NOT_FOUND 'Not Found' with no view data. Editor URL shows the 'not shared with you' message. ALT1's view keeps its name and row_version 1, not in the Recycle Bin; test user 1's list has no such view and no clone.</t>
+  </si>
+  <si>
+    <t>QA CV k3' on Leads. PATCH {module_id: Deals} -&gt; 200 but ignored (module stays Leads). GET/PATCH/DELETE under /modules/{Deals}/views/{v} -&gt; 404 each. GET under Leads -&gt; 200 'QA CV k3', module Leads; not listed among Deals views.</t>
+  </si>
+  <si>
+    <t>As test user 1: random UUID, the deleted 'QA CV k4-deleted' (in the Recycle Bin) and ALT1's private view all return 404 with the identical body {success:false, error NOT_FOUND 'Not Found'} and identical headers (ignoring date/request ids). Nothing distinguishes existing, deleted and private.</t>
+  </si>
+  <si>
+    <t>Test user 2 (profile 'test', no Manage Shared Views) created private 'QA CV k5' (201). PATCH visibility everyone -&gt; 403 PERMISSION_DENIED; PATCH selected + [ALT1] -&gt; 403. View stays private with no shared users; ALT1 does not see it.</t>
+  </si>
+  <si>
+    <t>Random user id part passes: PATCH 'QA CV k6' selected + 00000000-…-0001 -&gt; 422 shared_user_ids[0] unknown_principal 'User not found.'; POST 'QA CV k6-new' with it -&gt; 422, not created; k6 stays private with no shared users. The other-tenant user part was not run - the other-tenant account file was not cleared for use.</t>
+  </si>
+  <si>
+    <t>Precondition not met: no Deals pick list or number field is hidden from test user 1 (the fields in test user 1's Deals records equal ALT1's), so board-summary on hidden fields cannot be tried.</t>
+  </si>
+  <si>
+    <t>POST with a 1 MB name -&gt; 422 name too_long 'A view name may be at most 120 characters.'; POST 'QA CV k9-cols' with 10,000 columns -&gt; 422 settings.columns too_many 'A view may show at most 30 columns.'; PATCH 'QA CV k9' with 10,000 columns -&gt; 422, columns unchanged (2). No 500, no stack trace; GET views afterwards 200 in 393 ms.</t>
+  </si>
+  <si>
+    <t>OPTIONS preflight with Origin https://evil.example -&gt; 204 with no Access-Control-Allow-Origin/Credentials/Methods (a browser blocks the PATCH). Control Origin https://staging-crm.taviportal.com -&gt; ACAO echoed, methods PATCH. (https://crm.taviportal.com is not allowed on the staging API.)</t>
+  </si>
+  <si>
+    <t>Not run: needs a signed-in user of another tenant; the other-tenant account file (AnywareStagingTempAccounts.txt) was not cleared for use in this session.</t>
+  </si>
+  <si>
+    <t>Arabic UI: 'records' in the record count and the sort label's field/direction are not translated - ALT1 switched to Arabic (dir=rtl, lang=ar), restored to English afterwards. Translated: picker button 'طرق العرض المخصصة', picker items ('كل Leads*', 'Leads الخاصة بي*' …), editor ('طريقة عرض مخصصة جديدة لـ Leads', 'تحديد المعايير'), Manage page ('إدارة طرق العرض المخصصة لـ Leads'), Kanban/Split controls. Plurals in Shared To: 1 'مستخدم واحد', 2 'مستخدمان', 3 '3 مستخدمين' - correct forms (the '3' uses a Latin digit while dates use Arabic-Indic digits). FAIL - English left in the Arabic UI: the record count reads '٥٠ records' ('records' untranslated) and the toolbar sort label reads 'ترتيب: created_at desc' (raw field key and direction). Module and field names (Leads, Deals, Full Name) are tenant data and were not counted.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-L01-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Arabic session: document dir=rtl. Deals board 'QA CV deals-by-stage': first stage (test-01) is the right-most column (x 876), next ones run right to left (test-02 576, qualification 276 …). Leads Kanban 'QA CV لوحة': No Answer right-most, then Busy, Switched Off leftwards. Picker opens from the right side (dropdown layout; the account's tabs layout was not active). Direction icons were not individually inspected.</t>
+  </si>
+  <si>
+    <t>Arabic: header layout picker accessible name stays 'Layout'; 'records' untranslated - Deals board in Arabic: board layout picker 'التخطيط' (translated) but the header layout picker keeps the accessible name 'Layout'; the count reads '٥٠ records'. No pipeline picker and no 'Probability …%' in stage headers in either language (see I05), so those two labels cannot be checked. (Reproduced from 4 Oct.)</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-L03-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Keyboard: focus drops to &lt;body&gt; after 'Add criteria row'; picker list has no arrow-key navigation - Keyboard only: focus 'Custom views', Enter -&gt; focus moves to 'Search views'; typing filters; ArrowDown does NOT move into the list (focus stays in the search box); Tab reaches 'QA CV count' and Enter opens it. Editor: name typed, 'Filter by criteria' toggled with Space, 'Add criteria row' with Enter adds a row but focus is lost to the page body. 'Edit Pattern' opens with focus in the pattern box. Kanban card move by keyboard works (I13). FAIL: focus lost after 'Add criteria row'; no arrow-key navigation in the picker menu (reproduced from 4 Oct).</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-L04-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Kanban a11y names: card checkboxes reuse the column select-all name, column buttons lack the column name, drag announcements read UUIDs - Names present: Leads picker 'Custom views', Deals 'Choose a Kanban view', 'Collapse all columns'; 0 unnamed buttons; no 'Load more' (no column over 100). FAIL: (1) every card checkbox carries its column's select-all name ('Select all loaded records in qualification' ×35, negotiation ×10 …); (2) every column button is just 'Collapse column', without the column name; (3) the drag live region reads the record UUID ('77828678-… is over needs_analysis.') instead of the record name. (Reproduced from 4 Oct.)</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-L05-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>At 390 px the 'Create Lead' button is cut off at the right edge - Viewport 390x844 (dropdown picker layout): document scrollWidth 390 (no horizontal page scroll); picker button opens by tap and lists views; editor usable - 'QA CV mobile' with Full Name starts with 'QA CV L' saved (201), editor scrollWidth 390. FAIL: the 'Create Lead' / 'More create options' buttons are cut off at the right edge of the header (only 'Crea… Lea…' visible). The 4 Oct tabs-layout break (0 px wide tab list) was not re-checked because this account is in dropdown layout.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-L06-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Firefox: React ErrorBoundary console error from a lazy-loaded component during the view/Kanban flow - Same flow per browser (fresh sign-in each): picker search + switch to 'QA CV count'; create 'QA CV chrome/edge/firefox' (Full Name starts with 'QA CV L0') -&gt; 201, 9 rows; Kanban 'QA CV kb-status' QA CV L01 No Answer -&gt; Busy -&gt; No Answer (PATCH 200 ×2, final No Answer). Chrome 131.0.6778.205 and Edge 154.0.4258.53: identical, only the unrelated 403 on /telephony/status in the console. Firefox 153.0 (Playwright build): identical results but a React '[ErrorBoundary] … Lazy@unknown' console error (reproduced from 4 Oct). Sign-out step skipped (a new sign-in revokes the previous session anyway). Note: the staging bundle changed during the run (index-Bzy9m5yg.js).</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-L07-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Arabic session. List view 'QA CV عملاء' (criterion Full Name contains 'أحمد') and Leads Kanban 'QA CV لوحة' (Lead Status). Picker search 'عملاء' lists 'QA CV عملاء'; tab/selected view shows it; Manage custom views row 'QA CV عملاء'; editor title 'تعديل طريقة العرض المخصصة: QA CV عملاء'; results = QA CV L10 أحمد. Kanban columns run right to left (No Answer right-most) and the card 'QA CV L10 أحمد' is intact. Restored to English.</t>
+  </si>
+  <si>
+    <t>List first page p95 far above 1.5 s (Leads 9.1 s, Deals 3.3 s) - 20 reloads each, navigation -&gt; first row with content (Chromium, cache on, another operator active on the tenant). All Leads (128 records): p95 9125 ms, median 4122, min 2851, max 10116. All Deals (50 records): p95 3300 ms, median 2585, min 1945, max 3696. Target p95 &lt;= 1.5 s missed on both (4 Oct: Leads p95 6826, Deals 3885).</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-L08-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>Kanban headers + first cards p95 5.1 s (target 2 s) - Deals Kanban 'QA CV deals-by-stage' (Stage, Amount; 12 columns), 20 reloads until all column headers with Amount totals and at least one card are shown: p95 5100 ms, median 2290, min 1261, max 26045. Target 2 s p95 missed.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-L09-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>65 'QA CV perf-NN' views created via API, perf-01…15 pinned (15 pinned; 173 Leads list views in total). Picker open (click -&gt; search box + list stable 2 frames), 10 times: median 110 ms, max 133 ms (&lt; 500 ms). Search 'perf-4' -&gt; only perf-40…49 immediately; 'zzz' -&gt; 'No views match.' immediately. All 15 unpinned afterwards.</t>
+  </si>
+  <si>
+    <t>After sign-out/sign-in Leads does not reopen the working view the user had open - ALT1 'QA CV hot leads' = (Lead Status Interested OR Follow Up) AND Created Time in the last 7 days (Owner = me left out: the QA CV seeds belong to the Owner account) - 13 records (QA CV L05…L11, L16 …). Pinned. Open QA CV L05, browser Back: same view, 13 records. Pinned views group lists 'QA CV hot leads' after signing in again. FAIL: after signing out (session ended, sign-in form shown) and signing in again, Leads opens on 'QA CV count' (16 records) instead of the working view 'QA CV hot leads' - the view opened by link/back is not kept as the last-used view across sign-in.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-E2E-1-vs-zoho.png</t>
+  </si>
+  <si>
+    <t>ALT1 'QA CV team set' (Lead Status Interested, QA CV names) shared with test user 2 (no Manage Shared Views). Test user 2 sees 7 Interested QA CV leads; clones it (201), renames to 'QA CV team set clone' and sets Follow Up (200). Test user 2 opening Edit on the shared view gets 'You cannot edit this view' and no form. ALT1 changes the shared view to Busy (staging has no 'Contacted' status) -&gt; test user 2's shared view now shows the Busy leads (QA CV L02, L13, L14, P02); the clone still shows Follow Up (QA CV L11), stays private and is not visible to ALT1; ALT1's view unaffected by the clone edit.</t>
+  </si>
+  <si>
+    <t>QA CV feed' (Lead Status Interested, QA CV L names). Work Queue &gt; Add a queue &gt; Create Queue: Module Leads, Layout Standard, 'How should this queue choose its records?' Custom view = QA CV feed, name 'QA CV feed-queue', Only me -&gt; POST kind queue settings {source: view, view_id: feed} 201. Queue shows 7 records (Interested). Edited 'QA CV feed' to Follow Up -&gt; the same queue now shows 1 record (Follow Up); Work Queue tile 7 -&gt; 1 without recreating the queue.</t>
+  </si>
+  <si>
+    <t>Editor: 'QA CV recovery' with 3 rows; pattern '(1 and 2' -&gt; both Save buttons disabled with 'Brackets are not balanced.' and 'Save or cancel the pattern to continue' - nothing saved (spec wording 'Fix the criteria pattern…' differs). '(1 and 2) or 3' -&gt; saved (201, pattern stored). Two tabs on Edit: tab 1 changed a value and saved; tab 2 renamed and pressed Save -&gt; 'Someone else saved this view after you opened it. Reload to get the latest version — your unsaved changes will be lost.', no PATCH sent; Reload loads tab 1's version. Deleted (the editor has no delete action and the dropdown row-menu Delete does nothing, see G04, so via API 204) -&gt; Recycle Bin -&gt; Restore: exactly one 'QA CV recovery', same id, tab 1's settings (value 'QA CV L1', pattern '(1 and 2) or 3').</t>
+  </si>
+  <si>
+    <t>Deals 'QA CV deals-by-stage' (only one pipeline on the Standard layout), board scrolled 600 px right. Open QA CV D07 -&gt; browser Back, and again with the in-app back button: same Kanban view and layout restored; the board's horizontal scroll returns to 0. list-preferences: lastView kanban, lastKanbanViewId = the view (no lastKanbanPipelineId - single pipeline). Zoho (live, Deals Kanban, scrolled 600 px, open card, Back) also returns with scroll 0, so TAVI matches the reference; the case's scroll-restore expectation looks stricter than Zoho.</t>
+  </si>
+  <si>
+    <t>Deals Kanban 'QA CV pipeline' (Stage, Amount). QA CV D02 (9,999.99) moved qualification -&gt; negotiation (no transition dialog - D02 is outside the blueprint's entry criteria): qualification 35/5,516,962,114,653.99 -&gt; 34/5,516,962,104,654.00, negotiation 10/16,893,538,880.00 -&gt; 11/16,893,548,879.99 (moved by exactly D02's amount). Audit: Mahmoud Mohamed, stage qualification -&gt; negotiation. Open D02 and Back: same Kanban view and layout; scroll resets to 0 - Zoho does the same (checked live). D02 restored.</t>
+  </si>
+  <si>
+    <t>Filter: Company contains 'QA' -&gt; No Answer 1, Busy 1, Wrong Number 1, Interested 1 (cards loaded = header counts) = board-summary called with the same filters = list total 4. The board has no record search box; Zoho's Deals Kanban (checked live) has none either - only the global 'Search records' and the filter panel - so the search half of the case does not apply to this design.</t>
+  </si>
+  <si>
+    <t>A criterion on a field hidden from the viewer exposes its value in the view editor and the view API - Company is hidden from test user 1 (User profile). QA CV L03 temporarily owned by test user 1 (restored afterwards) so the record is visible but its Company is not. ALT1's 'QA CV k7' (Everyone) filters Company equals &lt;L03's company&gt;. As test user 1: the editor shows the banner 'Some fields in this view's criteria are deleted or hidden from you: company. The view still filters on them.' BUT the criterion row still displays the hidden field and its actual value (Company Equals 'شركة الأمل') in the value box; GET /modules/{Leads}/views/{k7} also returns settings.criteria with the value in plain text; and the grid shows QA CV L03 as the match - so test user 1 learns L03's hidden Company value from the UI and the API.</t>
+  </si>
+  <si>
+    <t>executions/execu_2026-10-05_11-20-40/bugs/screenshots/owner-112040-7855-K07-vs-zoho.png</t>
   </si>
 </sst>
 </file>
@@ -7869,7 +8160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -7920,9 +8211,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -16393,26 +16681,26 @@
       <c r="J1" s="11" t="s">
         <v>1876</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="L1" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="27" t="s">
+      <c r="M1" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="27" t="s">
+      <c r="O1" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="P1" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="Q1" s="27" t="s">
+      <c r="Q1" s="26" t="s">
         <v>1868</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>13</v>
       </c>
@@ -16435,39 +16723,39 @@
         <v>1878</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>1878</v>
+        <v>1886</v>
       </c>
       <c r="J2" s="12" t="s">
         <v>1878</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="20" t="s">
         <v>1877</v>
       </c>
-      <c r="M2" s="20">
+      <c r="M2" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$2,$E$2:$E$239,$M$1)</f>
-        <v>9</v>
-      </c>
-      <c r="N2" s="20">
+        <v>18</v>
+      </c>
+      <c r="N2" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$2,$E$2:$E$239,$N$1)</f>
-        <v>21</v>
-      </c>
-      <c r="O2" s="20">
+        <v>50</v>
+      </c>
+      <c r="O2" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$2,$E$2:$E$239,$O$1)</f>
-        <v>48</v>
-      </c>
-      <c r="P2" s="20">
+        <v>47</v>
+      </c>
+      <c r="P2" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$2,$E$2:$E$239,$P$1)</f>
         <v>4</v>
       </c>
-      <c r="Q2" s="20">
+      <c r="Q2" s="19">
         <f>COUNTIF($F$2:$F$239,$L$2)</f>
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>22</v>
       </c>
@@ -16483,46 +16771,46 @@
       <c r="E3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>1880</v>
+      <c r="F3" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H3" s="12" t="s">
+        <v>1885</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>1890</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>1878</v>
+      </c>
+      <c r="L3" s="21" t="s">
         <v>1879</v>
       </c>
-      <c r="I3" s="13" t="s">
-        <v>1881</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>1878</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>1880</v>
-      </c>
-      <c r="M3" s="20">
+      <c r="M3" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$3,$E$2:$E$239,$M$1)</f>
-        <v>5</v>
-      </c>
-      <c r="N3" s="20">
+        <v>7</v>
+      </c>
+      <c r="N3" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$3,$E$2:$E$239,$N$1)</f>
-        <v>6</v>
-      </c>
-      <c r="O3" s="20">
+        <v>15</v>
+      </c>
+      <c r="O3" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$3,$E$2:$E$239,$O$1)</f>
-        <v>16</v>
-      </c>
-      <c r="P3" s="20">
+        <v>17</v>
+      </c>
+      <c r="P3" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$3,$E$2:$E$239,$P$1)</f>
         <v>4</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="19">
         <f>COUNTIF($F$2:$F$239,$L$3)</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>30</v>
       </c>
@@ -16538,46 +16826,46 @@
       <c r="E4" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="14" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>1878</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>1885</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>1891</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>1878</v>
+      </c>
+      <c r="L4" s="22" t="s">
         <v>1880</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>2005</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>2006</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>2007</v>
-      </c>
-      <c r="L4" s="23" t="s">
-        <v>1882</v>
-      </c>
-      <c r="M4" s="20">
+      <c r="M4" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$4,$E$2:$E$239,$M$1)</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="20">
+        <v>11</v>
+      </c>
+      <c r="N4" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$4,$E$2:$E$239,$N$1)</f>
-        <v>0</v>
-      </c>
-      <c r="O4" s="20">
+        <v>2</v>
+      </c>
+      <c r="O4" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$4,$E$2:$E$239,$O$1)</f>
         <v>2</v>
       </c>
-      <c r="P4" s="20">
+      <c r="P4" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$4,$E$2:$E$239,$P$1)</f>
         <v>1</v>
       </c>
-      <c r="Q4" s="20">
+      <c r="Q4" s="19">
         <f>COUNTIF($F$2:$F$239,$L$4)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>39</v>
       </c>
@@ -16593,46 +16881,46 @@
       <c r="E5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>1880</v>
+      <c r="F5" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>19</v>
+        <v>1878</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>2005</v>
+        <v>1885</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>2008</v>
+        <v>1892</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>2009</v>
-      </c>
-      <c r="L5" s="24" t="s">
+        <v>1878</v>
+      </c>
+      <c r="L5" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="M5" s="20">
+      <c r="M5" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$5,$E$2:$E$239,$M$1)</f>
         <v>1</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$5,$E$2:$E$239,$N$1)</f>
         <v>18</v>
       </c>
-      <c r="O5" s="20">
+      <c r="O5" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$5,$E$2:$E$239,$O$1)</f>
         <v>18</v>
       </c>
-      <c r="P5" s="20">
+      <c r="P5" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$5,$E$2:$E$239,$P$1)</f>
         <v>23</v>
       </c>
-      <c r="Q5" s="20">
+      <c r="Q5" s="19">
         <f>COUNTIF($F$2:$F$239,$L$5)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>47</v>
       </c>
@@ -16655,39 +16943,39 @@
         <v>1878</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>1878</v>
+        <v>1893</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>1878</v>
       </c>
-      <c r="L6" s="25" t="s">
-        <v>1920</v>
-      </c>
-      <c r="M6" s="20">
+      <c r="L6" s="24" t="s">
+        <v>1883</v>
+      </c>
+      <c r="M6" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$6,$E$2:$E$239,$M$1)</f>
-        <v>22</v>
-      </c>
-      <c r="N6" s="20">
+        <v>0</v>
+      </c>
+      <c r="N6" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$6,$E$2:$E$239,$N$1)</f>
-        <v>40</v>
-      </c>
-      <c r="O6" s="20">
+        <v>0</v>
+      </c>
+      <c r="O6" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$6,$E$2:$E$239,$O$1)</f>
         <v>0</v>
       </c>
-      <c r="P6" s="20">
+      <c r="P6" s="19">
         <f>COUNTIFS($F$2:$F$239,$L$6,$E$2:$E$239,$P$1)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="20">
+      <c r="Q6" s="19">
         <f>COUNTIF($F$2:$F$239,$L$6)</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>55</v>
       </c>
@@ -16710,39 +16998,39 @@
         <v>1878</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>1879</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>1878</v>
+        <v>1885</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>1894</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>1878</v>
       </c>
-      <c r="L7" s="26" t="s">
+      <c r="L7" s="25" t="s">
         <v>1868</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="25">
         <f>SUM(M2:M6)</f>
         <v>37</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="25">
         <f>SUM(N2:N6)</f>
         <v>85</v>
       </c>
-      <c r="O7" s="26">
+      <c r="O7" s="25">
         <f>SUM(O2:O6)</f>
         <v>84</v>
       </c>
-      <c r="P7" s="26">
+      <c r="P7" s="25">
         <f>SUM(P2:P6)</f>
         <v>32</v>
       </c>
-      <c r="Q7" s="26">
+      <c r="Q7" s="25">
         <f>SUM(Q2:Q6)</f>
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>63</v>
       </c>
@@ -16765,16 +17053,16 @@
         <v>1878</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>1878</v>
+        <v>1895</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>71</v>
       </c>
@@ -16790,26 +17078,26 @@
       <c r="E9" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>1877</v>
+      <c r="F9" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>1878</v>
+        <v>1896</v>
       </c>
       <c r="J9" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="L9" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>79</v>
       </c>
@@ -16825,23 +17113,23 @@
       <c r="E10" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>1877</v>
+      <c r="F10" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>1878</v>
+        <v>1897</v>
       </c>
       <c r="J10" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="165" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="120" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>87</v>
       </c>
@@ -16857,23 +17145,23 @@
       <c r="E11" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="15" t="s">
-        <v>1880</v>
+      <c r="F11" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>1883</v>
+        <v>1904</v>
       </c>
       <c r="J11" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>95</v>
       </c>
@@ -16896,16 +17184,16 @@
         <v>1878</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>102</v>
       </c>
@@ -16928,16 +17216,16 @@
         <v>1878</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>1878</v>
+        <v>1888</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>110</v>
       </c>
@@ -16954,7 +17242,7 @@
         <v>116</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>1878</v>
@@ -16963,7 +17251,7 @@
         <v>1885</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>1878</v>
@@ -16992,7 +17280,7 @@
         <v>1878</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>1878</v>
@@ -17001,7 +17289,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>129</v>
       </c>
@@ -17027,13 +17315,13 @@
         <v>1885</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>1888</v>
+        <v>1898</v>
       </c>
       <c r="J16" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>138</v>
       </c>
@@ -17049,23 +17337,23 @@
       <c r="E17" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="F17" s="15" t="s">
-        <v>1880</v>
+      <c r="F17" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>116</v>
+        <v>1878</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>1885</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>146</v>
       </c>
@@ -17091,7 +17379,7 @@
         <v>1885</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>1891</v>
+        <v>1900</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>1878</v>
@@ -17123,13 +17411,13 @@
         <v>1885</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>1892</v>
+        <v>1905</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>162</v>
       </c>
@@ -17154,14 +17442,14 @@
       <c r="H20" s="12" t="s">
         <v>1885</v>
       </c>
-      <c r="I20" s="13" t="s">
-        <v>1893</v>
+      <c r="I20" s="18" t="s">
+        <v>1901</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>168</v>
       </c>
@@ -17184,16 +17472,16 @@
         <v>1878</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>1878</v>
+        <v>1906</v>
       </c>
       <c r="J21" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>175</v>
       </c>
@@ -17216,16 +17504,16 @@
         <v>1878</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>1878</v>
+        <v>1907</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>183</v>
       </c>
@@ -17241,23 +17529,23 @@
       <c r="E23" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="14" t="s">
-        <v>1877</v>
+      <c r="F23" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>1878</v>
+        <v>1908</v>
       </c>
       <c r="J23" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>191</v>
       </c>
@@ -17268,7 +17556,7 @@
         <v>190</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>1894</v>
+        <v>1882</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>19</v>
@@ -17280,16 +17568,16 @@
         <v>1878</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>1878</v>
+        <v>1902</v>
       </c>
       <c r="J24" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>197</v>
       </c>
@@ -17312,16 +17600,16 @@
         <v>1878</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>1878</v>
+        <v>1909</v>
       </c>
       <c r="J25" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>205</v>
       </c>
@@ -17347,13 +17635,13 @@
         <v>1885</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>1895</v>
+        <v>1910</v>
       </c>
       <c r="J26" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>213</v>
       </c>
@@ -17379,13 +17667,13 @@
         <v>1885</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>1896</v>
+        <v>1903</v>
       </c>
       <c r="J27" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>221</v>
       </c>
@@ -17402,22 +17690,22 @@
         <v>36</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>1897</v>
+        <v>1911</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>229</v>
       </c>
@@ -17434,7 +17722,7 @@
         <v>135</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>135</v>
@@ -17443,10 +17731,10 @@
         <v>1885</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>1898</v>
+        <v>1913</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>1899</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -17472,7 +17760,7 @@
         <v>1878</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>1878</v>
@@ -17481,7 +17769,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>246</v>
       </c>
@@ -17504,10 +17792,10 @@
         <v>1878</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>1878</v>
+        <v>1915</v>
       </c>
       <c r="J31" s="12" t="s">
         <v>1878</v>
@@ -17530,22 +17818,22 @@
         <v>19</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>1878</v>
+        <v>116</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>1900</v>
+        <v>1916</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>261</v>
       </c>
@@ -17571,13 +17859,13 @@
         <v>1885</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>1901</v>
+        <v>1918</v>
       </c>
       <c r="J33" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>269</v>
       </c>
@@ -17603,13 +17891,13 @@
         <v>1885</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>1902</v>
+        <v>1919</v>
       </c>
       <c r="J34" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>277</v>
       </c>
@@ -17635,13 +17923,13 @@
         <v>1885</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>1903</v>
+        <v>1920</v>
       </c>
       <c r="J35" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>284</v>
       </c>
@@ -17667,13 +17955,13 @@
         <v>1885</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>1904</v>
+        <v>1921</v>
       </c>
       <c r="J36" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>291</v>
       </c>
@@ -17699,13 +17987,13 @@
         <v>1885</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>1905</v>
+        <v>1937</v>
       </c>
       <c r="J37" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>298</v>
       </c>
@@ -17731,13 +18019,13 @@
         <v>1885</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>1906</v>
+        <v>1926</v>
       </c>
       <c r="J38" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>305</v>
       </c>
@@ -17754,22 +18042,22 @@
         <v>19</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>1878</v>
+        <v>116</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>1907</v>
+        <v>1934</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>312</v>
       </c>
@@ -17795,13 +18083,13 @@
         <v>1885</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>1908</v>
+        <v>1927</v>
       </c>
       <c r="J40" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>319</v>
       </c>
@@ -17827,13 +18115,13 @@
         <v>1885</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>1909</v>
+        <v>1928</v>
       </c>
       <c r="J41" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>326</v>
       </c>
@@ -17850,7 +18138,7 @@
         <v>135</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>116</v>
@@ -17859,13 +18147,13 @@
         <v>1885</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>1910</v>
+        <v>1929</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>1911</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>333</v>
       </c>
@@ -17888,10 +18176,10 @@
         <v>1878</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>1878</v>
+        <v>1938</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>1878</v>
@@ -17923,13 +18211,13 @@
         <v>1885</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>1912</v>
+        <v>1931</v>
       </c>
       <c r="J44" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>348</v>
       </c>
@@ -17952,16 +18240,16 @@
         <v>1878</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>1878</v>
+        <v>1939</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>356</v>
       </c>
@@ -17987,13 +18275,13 @@
         <v>1885</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>1913</v>
+        <v>1940</v>
       </c>
       <c r="J46" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
         <v>363</v>
       </c>
@@ -18019,13 +18307,13 @@
         <v>1885</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>1914</v>
+        <v>1932</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>370</v>
       </c>
@@ -18048,16 +18336,16 @@
         <v>1878</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>1878</v>
+        <v>1936</v>
       </c>
       <c r="J48" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>378</v>
       </c>
@@ -18083,13 +18371,13 @@
         <v>1885</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>1915</v>
+        <v>1933</v>
       </c>
       <c r="J49" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>385</v>
       </c>
@@ -18112,16 +18400,16 @@
         <v>1878</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>1879</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>1916</v>
+        <v>1885</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>1922</v>
       </c>
       <c r="J50" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
         <v>393</v>
       </c>
@@ -18144,16 +18432,16 @@
         <v>1878</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>1917</v>
+        <v>1923</v>
       </c>
       <c r="J51" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
         <v>401</v>
       </c>
@@ -18176,10 +18464,10 @@
         <v>1878</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>1918</v>
+        <v>1924</v>
       </c>
       <c r="J52" s="12" t="s">
         <v>1878</v>
@@ -18211,13 +18499,13 @@
         <v>1885</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>1919</v>
+        <v>1925</v>
       </c>
       <c r="J53" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
         <v>415</v>
       </c>
@@ -18233,23 +18521,23 @@
       <c r="E54" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F54" s="19" t="s">
-        <v>1920</v>
+      <c r="F54" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>1878</v>
+        <v>1941</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>423</v>
       </c>
@@ -18272,10 +18560,10 @@
         <v>1878</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>1921</v>
+        <v>1942</v>
       </c>
       <c r="J55" s="12" t="s">
         <v>1878</v>
@@ -18304,16 +18592,16 @@
         <v>1878</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>1922</v>
+        <v>1943</v>
       </c>
       <c r="J56" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
         <v>438</v>
       </c>
@@ -18336,16 +18624,16 @@
         <v>1878</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>1923</v>
+        <v>1944</v>
       </c>
       <c r="J57" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
         <v>446</v>
       </c>
@@ -18368,16 +18656,16 @@
         <v>1878</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>1924</v>
+        <v>1945</v>
       </c>
       <c r="J58" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>454</v>
       </c>
@@ -18394,22 +18682,22 @@
         <v>19</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>1925</v>
+        <v>1946</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
         <v>461</v>
       </c>
@@ -18432,16 +18720,16 @@
         <v>1878</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>1926</v>
+        <v>1948</v>
       </c>
       <c r="J60" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
         <v>468</v>
       </c>
@@ -18464,16 +18752,16 @@
         <v>1878</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>1927</v>
+        <v>1949</v>
       </c>
       <c r="J61" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>476</v>
       </c>
@@ -18490,22 +18778,22 @@
         <v>36</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>1878</v>
+        <v>19</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>1928</v>
+        <v>1950</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
         <v>484</v>
       </c>
@@ -18528,16 +18816,16 @@
         <v>1878</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>1929</v>
+        <v>1952</v>
       </c>
       <c r="J63" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
         <v>491</v>
       </c>
@@ -18563,13 +18851,13 @@
         <v>1885</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>1930</v>
+        <v>1953</v>
       </c>
       <c r="J64" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
         <v>498</v>
       </c>
@@ -18595,13 +18883,13 @@
         <v>1885</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>1931</v>
+        <v>1954</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
         <v>506</v>
       </c>
@@ -18627,13 +18915,13 @@
         <v>1885</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>1932</v>
+        <v>1955</v>
       </c>
       <c r="J66" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
         <v>513</v>
       </c>
@@ -18659,13 +18947,13 @@
         <v>1885</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>1933</v>
+        <v>1956</v>
       </c>
       <c r="J67" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
         <v>521</v>
       </c>
@@ -18682,7 +18970,7 @@
         <v>135</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G68" s="12" t="s">
         <v>116</v>
@@ -18691,13 +18979,13 @@
         <v>1885</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>1934</v>
+        <v>1957</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>1935</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
         <v>529</v>
       </c>
@@ -18720,10 +19008,10 @@
         <v>1878</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>1936</v>
+        <v>1959</v>
       </c>
       <c r="J69" s="12" t="s">
         <v>1878</v>
@@ -18746,22 +19034,22 @@
         <v>19</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>1937</v>
+        <v>1960</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
         <v>545</v>
       </c>
@@ -18784,16 +19072,16 @@
         <v>1878</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>1938</v>
+        <v>1962</v>
       </c>
       <c r="J71" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
         <v>553</v>
       </c>
@@ -18819,13 +19107,13 @@
         <v>1885</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>1939</v>
+        <v>1963</v>
       </c>
       <c r="J72" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
         <v>561</v>
       </c>
@@ -18842,22 +19130,22 @@
         <v>19</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>1940</v>
+        <v>1964</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
         <v>568</v>
       </c>
@@ -18880,16 +19168,16 @@
         <v>1878</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>1941</v>
+        <v>1966</v>
       </c>
       <c r="J74" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
         <v>575</v>
       </c>
@@ -18905,23 +19193,23 @@
       <c r="E75" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F75" s="19" t="s">
-        <v>1920</v>
+      <c r="F75" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>1878</v>
+        <v>116</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>1878</v>
+        <v>1967</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
         <v>583</v>
       </c>
@@ -18937,23 +19225,23 @@
       <c r="E76" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F76" s="19" t="s">
-        <v>1920</v>
+      <c r="F76" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>1878</v>
+        <v>116</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>1878</v>
+        <v>1969</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
         <v>590</v>
       </c>
@@ -18979,13 +19267,13 @@
         <v>1885</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>1942</v>
+        <v>1971</v>
       </c>
       <c r="J77" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
         <v>597</v>
       </c>
@@ -19002,7 +19290,7 @@
         <v>135</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>135</v>
@@ -19011,13 +19299,13 @@
         <v>1885</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>1943</v>
+        <v>1972</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
         <v>605</v>
       </c>
@@ -19034,7 +19322,7 @@
         <v>135</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G79" s="12" t="s">
         <v>135</v>
@@ -19043,13 +19331,13 @@
         <v>1885</v>
       </c>
       <c r="I79" s="18" t="s">
-        <v>1945</v>
+        <v>1974</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
         <v>614</v>
       </c>
@@ -19065,17 +19353,17 @@
       <c r="E80" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F80" s="19" t="s">
-        <v>1920</v>
+      <c r="F80" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G80" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>1878</v>
+        <v>1976</v>
       </c>
       <c r="J80" s="12" t="s">
         <v>1878</v>
@@ -19097,23 +19385,23 @@
       <c r="E81" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F81" s="19" t="s">
-        <v>1920</v>
+      <c r="F81" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>1878</v>
-      </c>
-      <c r="I81" s="13" t="s">
-        <v>1878</v>
+        <v>1885</v>
+      </c>
+      <c r="I81" s="18" t="s">
+        <v>1977</v>
       </c>
       <c r="J81" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
         <v>629</v>
       </c>
@@ -19129,17 +19417,17 @@
       <c r="E82" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F82" s="19" t="s">
-        <v>1920</v>
+      <c r="F82" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>1878</v>
+        <v>1978</v>
       </c>
       <c r="J82" s="12" t="s">
         <v>1878</v>
@@ -19171,13 +19459,13 @@
         <v>1885</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>1947</v>
+        <v>1979</v>
       </c>
       <c r="J83" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
         <v>644</v>
       </c>
@@ -19203,13 +19491,13 @@
         <v>1885</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>1948</v>
+        <v>1980</v>
       </c>
       <c r="J84" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
         <v>651</v>
       </c>
@@ -19235,13 +19523,13 @@
         <v>1885</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>1949</v>
+        <v>1981</v>
       </c>
       <c r="J85" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
         <v>658</v>
       </c>
@@ -19258,7 +19546,7 @@
         <v>116</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G86" s="12" t="s">
         <v>116</v>
@@ -19267,13 +19555,13 @@
         <v>1885</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>1950</v>
+        <v>1982</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
         <v>665</v>
       </c>
@@ -19299,13 +19587,13 @@
         <v>1885</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>1952</v>
+        <v>1984</v>
       </c>
       <c r="J87" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="165" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
         <v>672</v>
       </c>
@@ -19321,23 +19609,23 @@
       <c r="E88" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F88" s="19" t="s">
-        <v>1920</v>
+      <c r="F88" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>1878</v>
+        <v>1985</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
         <v>680</v>
       </c>
@@ -19353,23 +19641,23 @@
       <c r="E89" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F89" s="19" t="s">
-        <v>1920</v>
+      <c r="F89" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>1878</v>
+        <v>1987</v>
       </c>
       <c r="J89" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
         <v>688</v>
       </c>
@@ -19385,23 +19673,23 @@
       <c r="E90" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F90" s="19" t="s">
-        <v>1920</v>
+      <c r="F90" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>1878</v>
+        <v>1988</v>
       </c>
       <c r="J90" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
         <v>696</v>
       </c>
@@ -19417,23 +19705,23 @@
       <c r="E91" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F91" s="19" t="s">
-        <v>1920</v>
+      <c r="F91" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G91" s="12" t="s">
-        <v>1878</v>
+        <v>19</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>1878</v>
+        <v>1989</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
         <v>705</v>
       </c>
@@ -19449,23 +19737,23 @@
       <c r="E92" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F92" s="19" t="s">
-        <v>1920</v>
+      <c r="F92" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>1878</v>
+        <v>1991</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
         <v>713</v>
       </c>
@@ -19481,23 +19769,23 @@
       <c r="E93" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F93" s="19" t="s">
-        <v>1920</v>
+      <c r="F93" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H93" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>1878</v>
+        <v>1993</v>
       </c>
       <c r="J93" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
         <v>721</v>
       </c>
@@ -19513,23 +19801,23 @@
       <c r="E94" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F94" s="19" t="s">
-        <v>1920</v>
+      <c r="F94" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>1878</v>
+        <v>1994</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
         <v>729</v>
       </c>
@@ -19546,7 +19834,7 @@
         <v>116</v>
       </c>
       <c r="F95" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>116</v>
@@ -19555,13 +19843,13 @@
         <v>1885</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>1953</v>
+        <v>1996</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
         <v>736</v>
       </c>
@@ -19577,23 +19865,23 @@
       <c r="E96" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F96" s="19" t="s">
-        <v>1920</v>
+      <c r="F96" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>1878</v>
+        <v>1998</v>
       </c>
       <c r="J96" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
         <v>744</v>
       </c>
@@ -19610,7 +19898,7 @@
         <v>135</v>
       </c>
       <c r="F97" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G97" s="12" t="s">
         <v>116</v>
@@ -19619,13 +19907,13 @@
         <v>1885</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>1955</v>
+        <v>1999</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
         <v>752</v>
       </c>
@@ -19641,20 +19929,20 @@
       <c r="E98" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F98" s="19" t="s">
-        <v>1920</v>
+      <c r="F98" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G98" s="12" t="s">
-        <v>1878</v>
+        <v>116</v>
       </c>
       <c r="H98" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>1878</v>
+        <v>2001</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>1878</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -19673,23 +19961,23 @@
       <c r="E99" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F99" s="19" t="s">
-        <v>1920</v>
+      <c r="F99" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G99" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H99" s="12" t="s">
-        <v>1878</v>
-      </c>
-      <c r="I99" s="13" t="s">
-        <v>1878</v>
+        <v>1885</v>
+      </c>
+      <c r="I99" s="18" t="s">
+        <v>2003</v>
       </c>
       <c r="J99" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
         <v>767</v>
       </c>
@@ -19715,13 +20003,13 @@
         <v>1885</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>1957</v>
+        <v>2004</v>
       </c>
       <c r="J100" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
         <v>774</v>
       </c>
@@ -19737,23 +20025,23 @@
       <c r="E101" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="F101" s="14" t="s">
-        <v>1877</v>
+      <c r="F101" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H101" s="12" t="s">
         <v>1885</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>1958</v>
+        <v>2005</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
         <v>782</v>
       </c>
@@ -19769,17 +20057,17 @@
       <c r="E102" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F102" s="19" t="s">
-        <v>1920</v>
+      <c r="F102" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>1878</v>
-      </c>
-      <c r="I102" s="13" t="s">
-        <v>1878</v>
+        <v>1885</v>
+      </c>
+      <c r="I102" s="18" t="s">
+        <v>2007</v>
       </c>
       <c r="J102" s="12" t="s">
         <v>1878</v>
@@ -19808,7 +20096,7 @@
         <v>1878</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I103" s="13" t="s">
         <v>1878</v>
@@ -19817,7 +20105,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
         <v>798</v>
       </c>
@@ -19842,14 +20130,14 @@
       <c r="H104" s="12" t="s">
         <v>1885</v>
       </c>
-      <c r="I104" s="13" t="s">
-        <v>1959</v>
+      <c r="I104" s="18" t="s">
+        <v>2008</v>
       </c>
       <c r="J104" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
         <v>806</v>
       </c>
@@ -19865,23 +20153,23 @@
       <c r="E105" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F105" s="19" t="s">
-        <v>1920</v>
+      <c r="F105" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>1878</v>
+        <v>2009</v>
       </c>
       <c r="J105" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
         <v>814</v>
       </c>
@@ -19906,8 +20194,8 @@
       <c r="H106" s="12" t="s">
         <v>1885</v>
       </c>
-      <c r="I106" s="13" t="s">
-        <v>1960</v>
+      <c r="I106" s="18" t="s">
+        <v>2010</v>
       </c>
       <c r="J106" s="12" t="s">
         <v>1878</v>
@@ -19936,7 +20224,7 @@
         <v>1878</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I107" s="13" t="s">
         <v>1878</v>
@@ -19968,7 +20256,7 @@
         <v>1878</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I108" s="13" t="s">
         <v>1878</v>
@@ -20000,7 +20288,7 @@
         <v>1878</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I109" s="13" t="s">
         <v>1878</v>
@@ -20032,7 +20320,7 @@
         <v>1878</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I110" s="13" t="s">
         <v>1878</v>
@@ -20041,7 +20329,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="165" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
         <v>850</v>
       </c>
@@ -20057,23 +20345,23 @@
       <c r="E111" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F111" s="19" t="s">
-        <v>1920</v>
+      <c r="F111" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G111" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>1878</v>
+        <v>2011</v>
       </c>
       <c r="J111" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
         <v>858</v>
       </c>
@@ -20089,23 +20377,23 @@
       <c r="E112" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F112" s="19" t="s">
-        <v>1920</v>
+      <c r="F112" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G112" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H112" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>1878</v>
+        <v>2012</v>
       </c>
       <c r="J112" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
         <v>866</v>
       </c>
@@ -20121,23 +20409,23 @@
       <c r="E113" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F113" s="19" t="s">
-        <v>1920</v>
+      <c r="F113" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G113" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>1878</v>
+        <v>2013</v>
       </c>
       <c r="J113" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
         <v>873</v>
       </c>
@@ -20154,7 +20442,7 @@
         <v>135</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G114" s="12" t="s">
         <v>135</v>
@@ -20163,13 +20451,13 @@
         <v>1885</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>1961</v>
+        <v>2014</v>
       </c>
       <c r="J114" s="12" t="s">
-        <v>1962</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
         <v>881</v>
       </c>
@@ -20185,23 +20473,23 @@
       <c r="E115" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F115" s="19" t="s">
-        <v>1920</v>
+      <c r="F115" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G115" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>1878</v>
+        <v>2016</v>
       </c>
       <c r="J115" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
         <v>889</v>
       </c>
@@ -20218,7 +20506,7 @@
         <v>135</v>
       </c>
       <c r="F116" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G116" s="12" t="s">
         <v>135</v>
@@ -20227,13 +20515,13 @@
         <v>1885</v>
       </c>
       <c r="I116" s="13" t="s">
-        <v>1963</v>
+        <v>2017</v>
       </c>
       <c r="J116" s="12" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
         <v>897</v>
       </c>
@@ -20249,17 +20537,17 @@
       <c r="E117" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F117" s="19" t="s">
-        <v>1920</v>
+      <c r="F117" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I117" s="13" t="s">
-        <v>1878</v>
+        <v>2019</v>
       </c>
       <c r="J117" s="12" t="s">
         <v>1878</v>
@@ -20290,14 +20578,14 @@
       <c r="H118" s="12" t="s">
         <v>1885</v>
       </c>
-      <c r="I118" s="13" t="s">
-        <v>1965</v>
+      <c r="I118" s="18" t="s">
+        <v>2020</v>
       </c>
       <c r="J118" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
         <v>913</v>
       </c>
@@ -20313,17 +20601,17 @@
       <c r="E119" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F119" s="19" t="s">
-        <v>1920</v>
+      <c r="F119" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H119" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I119" s="13" t="s">
-        <v>1878</v>
+        <v>2021</v>
       </c>
       <c r="J119" s="12" t="s">
         <v>1878</v>
@@ -20352,7 +20640,7 @@
         <v>1878</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I120" s="13" t="s">
         <v>1878</v>
@@ -20361,7 +20649,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
         <v>928</v>
       </c>
@@ -20386,14 +20674,14 @@
       <c r="H121" s="12" t="s">
         <v>1885</v>
       </c>
-      <c r="I121" s="13" t="s">
-        <v>1966</v>
+      <c r="I121" s="18" t="s">
+        <v>2022</v>
       </c>
       <c r="J121" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
         <v>936</v>
       </c>
@@ -20409,23 +20697,23 @@
       <c r="E122" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F122" s="19" t="s">
-        <v>1920</v>
+      <c r="F122" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G122" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I122" s="13" t="s">
-        <v>1878</v>
+        <v>2023</v>
       </c>
       <c r="J122" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
         <v>944</v>
       </c>
@@ -20441,17 +20729,17 @@
       <c r="E123" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F123" s="19" t="s">
-        <v>1920</v>
+      <c r="F123" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H123" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>1878</v>
+        <v>2024</v>
       </c>
       <c r="J123" s="12" t="s">
         <v>1878</v>
@@ -20483,13 +20771,13 @@
         <v>1885</v>
       </c>
       <c r="I124" s="13" t="s">
-        <v>1967</v>
+        <v>2025</v>
       </c>
       <c r="J124" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
         <v>961</v>
       </c>
@@ -20505,23 +20793,23 @@
       <c r="E125" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F125" s="19" t="s">
-        <v>1920</v>
+      <c r="F125" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H125" s="12" t="s">
-        <v>1878</v>
-      </c>
-      <c r="I125" s="13" t="s">
-        <v>1878</v>
+        <v>1885</v>
+      </c>
+      <c r="I125" s="18" t="s">
+        <v>2026</v>
       </c>
       <c r="J125" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
         <v>969</v>
       </c>
@@ -20547,7 +20835,7 @@
         <v>1885</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>1968</v>
+        <v>2027</v>
       </c>
       <c r="J126" s="12" t="s">
         <v>1878</v>
@@ -20570,7 +20858,7 @@
         <v>135</v>
       </c>
       <c r="F127" s="16" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="G127" s="12" t="s">
         <v>1878</v>
@@ -20579,13 +20867,13 @@
         <v>1885</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>1969</v>
+        <v>2028</v>
       </c>
       <c r="J127" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
         <v>984</v>
       </c>
@@ -20601,20 +20889,20 @@
       <c r="E128" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F128" s="19" t="s">
-        <v>1920</v>
+      <c r="F128" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G128" s="12" t="s">
-        <v>1878</v>
+        <v>116</v>
       </c>
       <c r="H128" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I128" s="13" t="s">
-        <v>1878</v>
+        <v>2029</v>
       </c>
       <c r="J128" s="12" t="s">
-        <v>1878</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -20640,7 +20928,7 @@
         <v>1878</v>
       </c>
       <c r="H129" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>1878</v>
@@ -20649,7 +20937,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
         <v>999</v>
       </c>
@@ -20675,13 +20963,13 @@
         <v>1885</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>1970</v>
+        <v>2031</v>
       </c>
       <c r="J130" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
         <v>1006</v>
       </c>
@@ -20706,14 +20994,14 @@
       <c r="H131" s="12" t="s">
         <v>1885</v>
       </c>
-      <c r="I131" s="13" t="s">
-        <v>1971</v>
+      <c r="I131" s="18" t="s">
+        <v>2032</v>
       </c>
       <c r="J131" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
         <v>1014</v>
       </c>
@@ -20729,23 +21017,23 @@
       <c r="E132" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F132" s="19" t="s">
-        <v>1920</v>
+      <c r="F132" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I132" s="13" t="s">
-        <v>1878</v>
+        <v>2033</v>
       </c>
       <c r="J132" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
         <v>1022</v>
       </c>
@@ -20761,20 +21049,20 @@
       <c r="E133" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F133" s="19" t="s">
-        <v>1920</v>
+      <c r="F133" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G133" s="12" t="s">
-        <v>1878</v>
+        <v>116</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>1878</v>
+        <v>2034</v>
       </c>
       <c r="J133" s="12" t="s">
-        <v>1878</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="60" x14ac:dyDescent="0.25">
@@ -20803,13 +21091,13 @@
         <v>1885</v>
       </c>
       <c r="I134" s="18" t="s">
-        <v>1972</v>
+        <v>2036</v>
       </c>
       <c r="J134" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
         <v>1038</v>
       </c>
@@ -20825,17 +21113,17 @@
       <c r="E135" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F135" s="19" t="s">
-        <v>1920</v>
+      <c r="F135" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H135" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>1878</v>
+        <v>2037</v>
       </c>
       <c r="J135" s="12" t="s">
         <v>1878</v>
@@ -20867,13 +21155,13 @@
         <v>1885</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>1973</v>
+        <v>2038</v>
       </c>
       <c r="J136" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
         <v>1054</v>
       </c>
@@ -20890,7 +21178,7 @@
         <v>135</v>
       </c>
       <c r="F137" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>135</v>
@@ -20899,13 +21187,13 @@
         <v>1885</v>
       </c>
       <c r="I137" s="13" t="s">
-        <v>1974</v>
+        <v>2039</v>
       </c>
       <c r="J137" s="12" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
         <v>1063</v>
       </c>
@@ -20921,23 +21209,23 @@
       <c r="E138" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F138" s="19" t="s">
-        <v>1920</v>
+      <c r="F138" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I138" s="13" t="s">
-        <v>1878</v>
+        <v>2041</v>
       </c>
       <c r="J138" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
         <v>1071</v>
       </c>
@@ -20953,23 +21241,23 @@
       <c r="E139" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F139" s="19" t="s">
-        <v>1920</v>
+      <c r="F139" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G139" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I139" s="13" t="s">
-        <v>1878</v>
+        <v>2042</v>
       </c>
       <c r="J139" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
         <v>1079</v>
       </c>
@@ -20985,23 +21273,23 @@
       <c r="E140" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F140" s="19" t="s">
-        <v>1920</v>
+      <c r="F140" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G140" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I140" s="13" t="s">
-        <v>1878</v>
+        <v>2043</v>
       </c>
       <c r="J140" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
         <v>1087</v>
       </c>
@@ -21018,22 +21306,22 @@
         <v>135</v>
       </c>
       <c r="F141" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G141" s="12" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="H141" s="12" t="s">
         <v>1885</v>
       </c>
       <c r="I141" s="13" t="s">
-        <v>1976</v>
+        <v>2044</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="165" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
         <v>1095</v>
       </c>
@@ -21049,23 +21337,23 @@
       <c r="E142" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F142" s="19" t="s">
-        <v>1920</v>
+      <c r="F142" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G142" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I142" s="13" t="s">
-        <v>1878</v>
+        <v>2046</v>
       </c>
       <c r="J142" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
         <v>1103</v>
       </c>
@@ -21081,23 +21369,23 @@
       <c r="E143" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F143" s="19" t="s">
-        <v>1920</v>
+      <c r="F143" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G143" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H143" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I143" s="13" t="s">
-        <v>1878</v>
+        <v>2048</v>
       </c>
       <c r="J143" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
         <v>1111</v>
       </c>
@@ -21113,23 +21401,23 @@
       <c r="E144" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F144" s="19" t="s">
-        <v>1920</v>
+      <c r="F144" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G144" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H144" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I144" s="13" t="s">
-        <v>1878</v>
+        <v>2049</v>
       </c>
       <c r="J144" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
         <v>1119</v>
       </c>
@@ -21145,23 +21433,23 @@
       <c r="E145" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F145" s="19" t="s">
-        <v>1920</v>
+      <c r="F145" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G145" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H145" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I145" s="13" t="s">
-        <v>1878</v>
+        <v>2050</v>
       </c>
       <c r="J145" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
         <v>1127</v>
       </c>
@@ -21177,23 +21465,23 @@
       <c r="E146" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F146" s="19" t="s">
-        <v>1920</v>
+      <c r="F146" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G146" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H146" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I146" s="13" t="s">
-        <v>1878</v>
+        <v>2051</v>
       </c>
       <c r="J146" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
         <v>1135</v>
       </c>
@@ -21210,7 +21498,7 @@
         <v>135</v>
       </c>
       <c r="F147" s="16" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>1878</v>
@@ -21219,13 +21507,13 @@
         <v>1885</v>
       </c>
       <c r="I147" s="13" t="s">
-        <v>1978</v>
+        <v>2053</v>
       </c>
       <c r="J147" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
         <v>1143</v>
       </c>
@@ -21241,20 +21529,20 @@
       <c r="E148" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F148" s="19" t="s">
-        <v>1920</v>
+      <c r="F148" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G148" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H148" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I148" s="13" t="s">
-        <v>1878</v>
+        <v>2054</v>
       </c>
       <c r="J148" s="12" t="s">
-        <v>1878</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -21283,7 +21571,7 @@
         <v>1885</v>
       </c>
       <c r="I149" s="13" t="s">
-        <v>1979</v>
+        <v>2056</v>
       </c>
       <c r="J149" s="12" t="s">
         <v>1878</v>
@@ -21315,13 +21603,13 @@
         <v>1885</v>
       </c>
       <c r="I150" s="13" t="s">
-        <v>1980</v>
+        <v>2057</v>
       </c>
       <c r="J150" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A151" s="12" t="s">
         <v>1167</v>
       </c>
@@ -21347,13 +21635,13 @@
         <v>1885</v>
       </c>
       <c r="I151" s="13" t="s">
-        <v>1981</v>
+        <v>2058</v>
       </c>
       <c r="J151" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
         <v>1175</v>
       </c>
@@ -21379,13 +21667,13 @@
         <v>1885</v>
       </c>
       <c r="I152" s="13" t="s">
-        <v>1982</v>
+        <v>2059</v>
       </c>
       <c r="J152" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
         <v>1183</v>
       </c>
@@ -21411,13 +21699,13 @@
         <v>1885</v>
       </c>
       <c r="I153" s="13" t="s">
-        <v>1983</v>
+        <v>2060</v>
       </c>
       <c r="J153" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
         <v>1191</v>
       </c>
@@ -21433,17 +21721,17 @@
       <c r="E154" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F154" s="19" t="s">
-        <v>1920</v>
+      <c r="F154" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G154" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H154" s="12" t="s">
-        <v>1878</v>
-      </c>
-      <c r="I154" s="13" t="s">
-        <v>1878</v>
+        <v>1885</v>
+      </c>
+      <c r="I154" s="18" t="s">
+        <v>2061</v>
       </c>
       <c r="J154" s="12" t="s">
         <v>1878</v>
@@ -21475,13 +21763,13 @@
         <v>1885</v>
       </c>
       <c r="I155" s="13" t="s">
-        <v>1984</v>
+        <v>2062</v>
       </c>
       <c r="J155" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
         <v>1207</v>
       </c>
@@ -21497,23 +21785,23 @@
       <c r="E156" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F156" s="19" t="s">
-        <v>1920</v>
+      <c r="F156" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G156" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H156" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I156" s="13" t="s">
-        <v>1878</v>
+        <v>2102</v>
       </c>
       <c r="J156" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A157" s="12" t="s">
         <v>1215</v>
       </c>
@@ -21529,17 +21817,17 @@
       <c r="E157" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F157" s="19" t="s">
-        <v>1920</v>
+      <c r="F157" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G157" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H157" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I157" s="13" t="s">
-        <v>1878</v>
+        <v>2104</v>
       </c>
       <c r="J157" s="12" t="s">
         <v>1878</v>
@@ -21571,13 +21859,13 @@
         <v>1885</v>
       </c>
       <c r="I158" s="13" t="s">
-        <v>1985</v>
+        <v>2063</v>
       </c>
       <c r="J158" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
         <v>1231</v>
       </c>
@@ -21593,23 +21881,23 @@
       <c r="E159" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F159" s="19" t="s">
-        <v>1920</v>
+      <c r="F159" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H159" s="12" t="s">
-        <v>1878</v>
-      </c>
-      <c r="I159" s="13" t="s">
-        <v>1878</v>
+        <v>1885</v>
+      </c>
+      <c r="I159" s="18" t="s">
+        <v>2064</v>
       </c>
       <c r="J159" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
         <v>1238</v>
       </c>
@@ -21625,23 +21913,23 @@
       <c r="E160" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="F160" s="14" t="s">
-        <v>1877</v>
+      <c r="F160" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>1878</v>
+        <v>116</v>
       </c>
       <c r="H160" s="12" t="s">
         <v>1885</v>
       </c>
       <c r="I160" s="13" t="s">
-        <v>1986</v>
+        <v>2065</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
         <v>1245</v>
       </c>
@@ -21667,7 +21955,7 @@
         <v>1885</v>
       </c>
       <c r="I161" s="13" t="s">
-        <v>1987</v>
+        <v>2067</v>
       </c>
       <c r="J161" s="12" t="s">
         <v>1878</v>
@@ -21696,7 +21984,7 @@
         <v>1878</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I162" s="13" t="s">
         <v>1878</v>
@@ -21705,7 +21993,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
         <v>1261</v>
       </c>
@@ -21721,23 +22009,23 @@
       <c r="E163" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F163" s="19" t="s">
-        <v>1920</v>
+      <c r="F163" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G163" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H163" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I163" s="13" t="s">
-        <v>1878</v>
+        <v>2068</v>
       </c>
       <c r="J163" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
         <v>1269</v>
       </c>
@@ -21753,23 +22041,23 @@
       <c r="E164" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F164" s="19" t="s">
-        <v>1920</v>
+      <c r="F164" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G164" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H164" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I164" s="13" t="s">
-        <v>1878</v>
+        <v>2069</v>
       </c>
       <c r="J164" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
         <v>1277</v>
       </c>
@@ -21785,23 +22073,23 @@
       <c r="E165" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F165" s="19" t="s">
-        <v>1920</v>
+      <c r="F165" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H165" s="12" t="s">
-        <v>1878</v>
-      </c>
-      <c r="I165" s="13" t="s">
-        <v>1878</v>
+        <v>1885</v>
+      </c>
+      <c r="I165" s="18" t="s">
+        <v>2070</v>
       </c>
       <c r="J165" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
         <v>1284</v>
       </c>
@@ -21817,23 +22105,23 @@
       <c r="E166" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F166" s="19" t="s">
-        <v>1920</v>
+      <c r="F166" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G166" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I166" s="13" t="s">
-        <v>1878</v>
+        <v>2071</v>
       </c>
       <c r="J166" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
         <v>1292</v>
       </c>
@@ -21849,23 +22137,23 @@
       <c r="E167" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F167" s="19" t="s">
-        <v>1920</v>
+      <c r="F167" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H167" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I167" s="13" t="s">
-        <v>1878</v>
+        <v>2072</v>
       </c>
       <c r="J167" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
         <v>1300</v>
       </c>
@@ -21881,23 +22169,23 @@
       <c r="E168" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F168" s="19" t="s">
-        <v>1920</v>
+      <c r="F168" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H168" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I168" s="13" t="s">
-        <v>1878</v>
+        <v>2073</v>
       </c>
       <c r="J168" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" ht="165" x14ac:dyDescent="0.25">
       <c r="A169" s="12" t="s">
         <v>1308</v>
       </c>
@@ -21913,23 +22201,23 @@
       <c r="E169" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F169" s="19" t="s">
-        <v>1920</v>
+      <c r="F169" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G169" s="12" t="s">
-        <v>1878</v>
+        <v>19</v>
       </c>
       <c r="H169" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I169" s="13" t="s">
-        <v>1878</v>
+        <v>2105</v>
       </c>
       <c r="J169" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
         <v>1316</v>
       </c>
@@ -21945,23 +22233,23 @@
       <c r="E170" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F170" s="19" t="s">
-        <v>1920</v>
+      <c r="F170" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G170" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H170" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I170" s="13" t="s">
-        <v>1878</v>
+        <v>2074</v>
       </c>
       <c r="J170" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A171" s="12" t="s">
         <v>1324</v>
       </c>
@@ -21977,23 +22265,23 @@
       <c r="E171" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F171" s="19" t="s">
-        <v>1920</v>
+      <c r="F171" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G171" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H171" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I171" s="13" t="s">
-        <v>1878</v>
+        <v>2075</v>
       </c>
       <c r="J171" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
         <v>1332</v>
       </c>
@@ -22009,23 +22297,23 @@
       <c r="E172" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F172" s="19" t="s">
-        <v>1920</v>
+      <c r="F172" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G172" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H172" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I172" s="13" t="s">
-        <v>1878</v>
+        <v>2076</v>
       </c>
       <c r="J172" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
         <v>1340</v>
       </c>
@@ -22041,23 +22329,23 @@
       <c r="E173" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F173" s="19" t="s">
-        <v>1920</v>
+      <c r="F173" s="16" t="s">
+        <v>1880</v>
       </c>
       <c r="G173" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H173" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I173" s="13" t="s">
-        <v>1878</v>
+        <v>2077</v>
       </c>
       <c r="J173" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" ht="165" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
         <v>1349</v>
       </c>
@@ -22073,23 +22361,23 @@
       <c r="E174" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F174" s="19" t="s">
-        <v>1920</v>
+      <c r="F174" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G174" s="12" t="s">
-        <v>1878</v>
+        <v>116</v>
       </c>
       <c r="H174" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I174" s="13" t="s">
-        <v>1878</v>
+        <v>2078</v>
       </c>
       <c r="J174" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A175" s="12" t="s">
         <v>1357</v>
       </c>
@@ -22105,23 +22393,23 @@
       <c r="E175" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F175" s="19" t="s">
-        <v>1920</v>
+      <c r="F175" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G175" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H175" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I175" s="13" t="s">
-        <v>1878</v>
+        <v>2080</v>
       </c>
       <c r="J175" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
         <v>1365</v>
       </c>
@@ -22138,7 +22426,7 @@
         <v>135</v>
       </c>
       <c r="F176" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G176" s="12" t="s">
         <v>116</v>
@@ -22147,13 +22435,13 @@
         <v>1885</v>
       </c>
       <c r="I176" s="13" t="s">
-        <v>1988</v>
+        <v>2081</v>
       </c>
       <c r="J176" s="12" t="s">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A177" s="12" t="s">
         <v>1373</v>
       </c>
@@ -22170,7 +22458,7 @@
         <v>135</v>
       </c>
       <c r="F177" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>116</v>
@@ -22179,13 +22467,13 @@
         <v>1885</v>
       </c>
       <c r="I177" s="13" t="s">
-        <v>1990</v>
+        <v>2083</v>
       </c>
       <c r="J177" s="12" t="s">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
         <v>1381</v>
       </c>
@@ -22202,7 +22490,7 @@
         <v>135</v>
       </c>
       <c r="F178" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G178" s="12" t="s">
         <v>116</v>
@@ -22211,13 +22499,13 @@
         <v>1885</v>
       </c>
       <c r="I178" s="13" t="s">
-        <v>1992</v>
+        <v>2085</v>
       </c>
       <c r="J178" s="12" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A179" s="12" t="s">
         <v>1389</v>
       </c>
@@ -22234,22 +22522,22 @@
         <v>135</v>
       </c>
       <c r="F179" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G179" s="12" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="H179" s="12" t="s">
         <v>1885</v>
       </c>
       <c r="I179" s="13" t="s">
-        <v>1994</v>
+        <v>2087</v>
       </c>
       <c r="J179" s="12" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="165" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
         <v>1397</v>
       </c>
@@ -22266,7 +22554,7 @@
         <v>135</v>
       </c>
       <c r="F180" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>116</v>
@@ -22275,13 +22563,13 @@
         <v>1885</v>
       </c>
       <c r="I180" s="13" t="s">
-        <v>1996</v>
+        <v>2089</v>
       </c>
       <c r="J180" s="12" t="s">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A181" s="12" t="s">
         <v>1405</v>
       </c>
@@ -22298,22 +22586,22 @@
         <v>116</v>
       </c>
       <c r="F181" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G181" s="12" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="H181" s="12" t="s">
         <v>1885</v>
       </c>
       <c r="I181" s="13" t="s">
-        <v>1998</v>
+        <v>2092</v>
       </c>
       <c r="J181" s="12" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
         <v>1413</v>
       </c>
@@ -22330,19 +22618,19 @@
         <v>116</v>
       </c>
       <c r="F182" s="15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G182" s="12" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="H182" s="12" t="s">
         <v>1885</v>
       </c>
       <c r="I182" s="13" t="s">
-        <v>2000</v>
+        <v>2094</v>
       </c>
       <c r="J182" s="12" t="s">
-        <v>2001</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="75" x14ac:dyDescent="0.25">
@@ -22371,13 +22659,13 @@
         <v>1885</v>
       </c>
       <c r="I183" s="13" t="s">
-        <v>2002</v>
+        <v>2096</v>
       </c>
       <c r="J183" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
         <v>1430</v>
       </c>
@@ -22393,23 +22681,23 @@
       <c r="E184" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F184" s="19" t="s">
-        <v>1920</v>
+      <c r="F184" s="15" t="s">
+        <v>1879</v>
       </c>
       <c r="G184" s="12" t="s">
-        <v>1878</v>
+        <v>135</v>
       </c>
       <c r="H184" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I184" s="13" t="s">
-        <v>1878</v>
+        <v>2097</v>
       </c>
       <c r="J184" s="12" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A185" s="12" t="s">
         <v>1438</v>
       </c>
@@ -22425,23 +22713,23 @@
       <c r="E185" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F185" s="19" t="s">
-        <v>1920</v>
+      <c r="F185" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H185" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I185" s="13" t="s">
-        <v>1878</v>
+        <v>2099</v>
       </c>
       <c r="J185" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
         <v>1446</v>
       </c>
@@ -22457,23 +22745,23 @@
       <c r="E186" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F186" s="19" t="s">
-        <v>1920</v>
+      <c r="F186" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H186" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I186" s="13" t="s">
-        <v>1878</v>
+        <v>2103</v>
       </c>
       <c r="J186" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
         <v>1454</v>
       </c>
@@ -22489,23 +22777,23 @@
       <c r="E187" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F187" s="19" t="s">
-        <v>1920</v>
+      <c r="F187" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G187" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H187" s="12" t="s">
-        <v>1878</v>
-      </c>
-      <c r="I187" s="13" t="s">
-        <v>1878</v>
+        <v>1885</v>
+      </c>
+      <c r="I187" s="18" t="s">
+        <v>2100</v>
       </c>
       <c r="J187" s="12" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" ht="165" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
         <v>1462</v>
       </c>
@@ -22521,17 +22809,17 @@
       <c r="E188" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F188" s="19" t="s">
-        <v>1920</v>
+      <c r="F188" s="14" t="s">
+        <v>1877</v>
       </c>
       <c r="G188" s="12" t="s">
         <v>1878</v>
       </c>
       <c r="H188" s="12" t="s">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="I188" s="13" t="s">
-        <v>1878</v>
+        <v>2101</v>
       </c>
       <c r="J188" s="12" t="s">
         <v>1878</v>
@@ -22563,7 +22851,7 @@
         <v>1885</v>
       </c>
       <c r="I189" s="13" t="s">
-        <v>2003</v>
+        <v>2091</v>
       </c>
       <c r="J189" s="12" t="s">
         <v>1878</v>
@@ -22592,7 +22880,7 @@
         <v>1878</v>
       </c>
       <c r="H190" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I190" s="13" t="s">
         <v>1878</v>
@@ -22624,7 +22912,7 @@
         <v>1878</v>
       </c>
       <c r="H191" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I191" s="13" t="s">
         <v>1878</v>
@@ -22656,7 +22944,7 @@
         <v>1878</v>
       </c>
       <c r="H192" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I192" s="13" t="s">
         <v>1878</v>
@@ -22688,7 +22976,7 @@
         <v>1878</v>
       </c>
       <c r="H193" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I193" s="13" t="s">
         <v>1878</v>
@@ -22720,7 +23008,7 @@
         <v>1878</v>
       </c>
       <c r="H194" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I194" s="13" t="s">
         <v>1878</v>
@@ -22752,7 +23040,7 @@
         <v>1878</v>
       </c>
       <c r="H195" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I195" s="13" t="s">
         <v>1878</v>
@@ -22784,7 +23072,7 @@
         <v>1878</v>
       </c>
       <c r="H196" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I196" s="13" t="s">
         <v>1878</v>
@@ -22816,7 +23104,7 @@
         <v>1878</v>
       </c>
       <c r="H197" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I197" s="13" t="s">
         <v>1878</v>
@@ -22848,7 +23136,7 @@
         <v>1878</v>
       </c>
       <c r="H198" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I198" s="13" t="s">
         <v>1878</v>
@@ -22880,7 +23168,7 @@
         <v>1878</v>
       </c>
       <c r="H199" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I199" s="13" t="s">
         <v>1878</v>
@@ -22912,7 +23200,7 @@
         <v>1878</v>
       </c>
       <c r="H200" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I200" s="13" t="s">
         <v>1878</v>
@@ -22944,7 +23232,7 @@
         <v>1878</v>
       </c>
       <c r="H201" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I201" s="13" t="s">
         <v>1878</v>
@@ -22976,7 +23264,7 @@
         <v>1878</v>
       </c>
       <c r="H202" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I202" s="13" t="s">
         <v>1878</v>
@@ -23008,7 +23296,7 @@
         <v>1878</v>
       </c>
       <c r="H203" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I203" s="13" t="s">
         <v>1878</v>
@@ -23040,7 +23328,7 @@
         <v>1878</v>
       </c>
       <c r="H204" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I204" s="13" t="s">
         <v>1878</v>
@@ -23072,7 +23360,7 @@
         <v>1878</v>
       </c>
       <c r="H205" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I205" s="13" t="s">
         <v>1878</v>
@@ -23104,7 +23392,7 @@
         <v>1878</v>
       </c>
       <c r="H206" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I206" s="13" t="s">
         <v>1878</v>
@@ -23136,7 +23424,7 @@
         <v>1878</v>
       </c>
       <c r="H207" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I207" s="13" t="s">
         <v>1878</v>
@@ -23168,7 +23456,7 @@
         <v>1878</v>
       </c>
       <c r="H208" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I208" s="13" t="s">
         <v>1878</v>
@@ -23200,7 +23488,7 @@
         <v>1878</v>
       </c>
       <c r="H209" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I209" s="13" t="s">
         <v>1878</v>
@@ -23232,7 +23520,7 @@
         <v>1878</v>
       </c>
       <c r="H210" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I210" s="13" t="s">
         <v>1878</v>
@@ -23264,7 +23552,7 @@
         <v>1878</v>
       </c>
       <c r="H211" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I211" s="13" t="s">
         <v>1878</v>
@@ -23296,7 +23584,7 @@
         <v>1878</v>
       </c>
       <c r="H212" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I212" s="13" t="s">
         <v>1878</v>
@@ -23328,7 +23616,7 @@
         <v>1878</v>
       </c>
       <c r="H213" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I213" s="13" t="s">
         <v>1878</v>
@@ -23360,7 +23648,7 @@
         <v>1878</v>
       </c>
       <c r="H214" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I214" s="13" t="s">
         <v>1878</v>
@@ -23392,7 +23680,7 @@
         <v>1878</v>
       </c>
       <c r="H215" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I215" s="13" t="s">
         <v>1878</v>
@@ -23424,7 +23712,7 @@
         <v>1878</v>
       </c>
       <c r="H216" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I216" s="13" t="s">
         <v>1878</v>
@@ -23456,7 +23744,7 @@
         <v>1878</v>
       </c>
       <c r="H217" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I217" s="13" t="s">
         <v>1878</v>
@@ -23488,7 +23776,7 @@
         <v>1878</v>
       </c>
       <c r="H218" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I218" s="13" t="s">
         <v>1878</v>
@@ -23520,7 +23808,7 @@
         <v>1878</v>
       </c>
       <c r="H219" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I219" s="13" t="s">
         <v>1878</v>
@@ -23552,7 +23840,7 @@
         <v>1878</v>
       </c>
       <c r="H220" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I220" s="13" t="s">
         <v>1878</v>
@@ -23584,7 +23872,7 @@
         <v>1878</v>
       </c>
       <c r="H221" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I221" s="13" t="s">
         <v>1878</v>
@@ -23616,7 +23904,7 @@
         <v>1878</v>
       </c>
       <c r="H222" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I222" s="13" t="s">
         <v>1878</v>
@@ -23648,7 +23936,7 @@
         <v>1878</v>
       </c>
       <c r="H223" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I223" s="13" t="s">
         <v>1878</v>
@@ -23680,7 +23968,7 @@
         <v>1878</v>
       </c>
       <c r="H224" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I224" s="13" t="s">
         <v>1878</v>
@@ -23712,7 +24000,7 @@
         <v>1878</v>
       </c>
       <c r="H225" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I225" s="13" t="s">
         <v>1878</v>
@@ -23744,7 +24032,7 @@
         <v>1878</v>
       </c>
       <c r="H226" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I226" s="13" t="s">
         <v>1878</v>
@@ -23776,7 +24064,7 @@
         <v>1878</v>
       </c>
       <c r="H227" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I227" s="13" t="s">
         <v>1878</v>
@@ -23808,7 +24096,7 @@
         <v>1878</v>
       </c>
       <c r="H228" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I228" s="13" t="s">
         <v>1878</v>
@@ -23840,7 +24128,7 @@
         <v>1878</v>
       </c>
       <c r="H229" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I229" s="13" t="s">
         <v>1878</v>
@@ -23872,7 +24160,7 @@
         <v>1878</v>
       </c>
       <c r="H230" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I230" s="13" t="s">
         <v>1878</v>
@@ -23904,7 +24192,7 @@
         <v>1878</v>
       </c>
       <c r="H231" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I231" s="13" t="s">
         <v>1878</v>
@@ -23936,7 +24224,7 @@
         <v>1878</v>
       </c>
       <c r="H232" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I232" s="13" t="s">
         <v>1878</v>
@@ -23968,7 +24256,7 @@
         <v>1878</v>
       </c>
       <c r="H233" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I233" s="13" t="s">
         <v>1878</v>
@@ -24000,7 +24288,7 @@
         <v>1878</v>
       </c>
       <c r="H234" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I234" s="13" t="s">
         <v>1878</v>
@@ -24032,7 +24320,7 @@
         <v>1878</v>
       </c>
       <c r="H235" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I235" s="13" t="s">
         <v>1878</v>
@@ -24064,7 +24352,7 @@
         <v>1878</v>
       </c>
       <c r="H236" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I236" s="13" t="s">
         <v>1878</v>
@@ -24096,7 +24384,7 @@
         <v>1878</v>
       </c>
       <c r="H237" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I237" s="13" t="s">
         <v>1878</v>
@@ -24128,7 +24416,7 @@
         <v>1878</v>
       </c>
       <c r="H238" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I238" s="13" t="s">
         <v>1878</v>
@@ -24160,7 +24448,7 @@
         <v>1878</v>
       </c>
       <c r="H239" s="12" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="I239" s="13" t="s">
         <v>1878</v>
